--- a/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
+++ b/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Develop\others\MyPGEE\main\408\ds\【数据结构应用题】打卡表及参考文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6146B23-BFD4-4B83-A31B-C7A03CA4B6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0469145-9C58-441D-895E-A2F98496F418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2162,95 +2162,11 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2287,6 +2203,90 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2653,13 +2653,13 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="53" t="s">
         <v>254</v>
       </c>
       <c r="D3" s="14" t="s">
@@ -2676,9 +2676,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.4">
-      <c r="A4" s="87"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="62"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="14" t="s">
         <v>12</v>
       </c>
@@ -2691,9 +2691,9 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
-      <c r="A5" s="87"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="62"/>
+      <c r="A5" s="59"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="14" t="s">
         <v>14</v>
       </c>
@@ -2706,9 +2706,9 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" ht="15.4">
-      <c r="A6" s="87"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="62"/>
+      <c r="A6" s="59"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
@@ -2721,9 +2721,9 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" ht="15.4">
-      <c r="A7" s="87"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="62"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="14" t="s">
         <v>18</v>
       </c>
@@ -2736,9 +2736,9 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" ht="15.4">
-      <c r="A8" s="88"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="82"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="14" t="s">
         <v>20</v>
       </c>
@@ -2751,9 +2751,9 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="62"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="14" t="s">
         <v>22</v>
       </c>
@@ -2766,9 +2766,9 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" ht="15.4">
-      <c r="A10" s="87"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="62"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="14" t="s">
         <v>24</v>
       </c>
@@ -2781,9 +2781,9 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" ht="15.4">
-      <c r="A11" s="87"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="62"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="47"/>
       <c r="D11" s="14" t="s">
         <v>26</v>
       </c>
@@ -2796,9 +2796,9 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" ht="15.4">
-      <c r="A12" s="87"/>
-      <c r="B12" s="84"/>
-      <c r="C12" s="62"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="14" t="s">
         <v>28</v>
       </c>
@@ -2811,9 +2811,9 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" ht="15.4">
-      <c r="A13" s="87"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="62"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="14" t="s">
         <v>30</v>
       </c>
@@ -2826,9 +2826,9 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7" ht="15.4">
-      <c r="A14" s="87"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="75" t="s">
+      <c r="A14" s="59"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="46" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -2840,14 +2840,14 @@
       <c r="F14" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G14" s="77" t="s">
+      <c r="G14" s="49" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.4">
-      <c r="A15" s="87"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="62"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="13" t="s">
         <v>36</v>
       </c>
@@ -2857,12 +2857,12 @@
       <c r="F15" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G15" s="62"/>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="1:7" ht="15.4">
-      <c r="A16" s="88"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="76"/>
+      <c r="A16" s="60"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="13" t="s">
         <v>38</v>
       </c>
@@ -2872,12 +2872,12 @@
       <c r="F16" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G16" s="78"/>
+      <c r="G16" s="50"/>
     </row>
     <row r="17" spans="1:15" ht="15.4">
-      <c r="A17" s="88"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="76"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
@@ -2887,12 +2887,12 @@
       <c r="F17" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G17" s="78"/>
+      <c r="G17" s="50"/>
     </row>
     <row r="18" spans="1:15" ht="15.4">
-      <c r="A18" s="87"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="62"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="47"/>
       <c r="D18" s="13" t="s">
         <v>42</v>
       </c>
@@ -2902,16 +2902,16 @@
       <c r="F18" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G18" s="62"/>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" spans="1:15" ht="16.149999999999999">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="74" t="s">
         <v>285</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="76" t="s">
         <v>284</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="77" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="20" t="s">
@@ -2923,22 +2923,22 @@
       <c r="F19" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G19" s="60" t="s">
+      <c r="G19" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="49"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="85"/>
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
       <c r="M19" s="22"/>
       <c r="N19" s="23"/>
-      <c r="O19" s="46"/>
+      <c r="O19" s="82"/>
     </row>
     <row r="20" spans="1:15" ht="15.4">
-      <c r="A20" s="56"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="59"/>
+      <c r="A20" s="75"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="78"/>
       <c r="D20" s="24" t="s">
         <v>46</v>
       </c>
@@ -2948,20 +2948,20 @@
       <c r="F20" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G20" s="56"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="83"/>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="22"/>
       <c r="N20" s="23"/>
-      <c r="O20" s="47"/>
+      <c r="O20" s="83"/>
     </row>
     <row r="21" spans="1:15" ht="15.4">
-      <c r="A21" s="56"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="59"/>
+      <c r="A21" s="75"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="78"/>
       <c r="D21" s="24" t="s">
         <v>48</v>
       </c>
@@ -2971,20 +2971,20 @@
       <c r="F21" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G21" s="56"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="83"/>
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
       <c r="M21" s="22"/>
       <c r="N21" s="23"/>
-      <c r="O21" s="47"/>
+      <c r="O21" s="83"/>
     </row>
     <row r="22" spans="1:15" ht="15.4">
-      <c r="A22" s="56"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="59"/>
+      <c r="A22" s="75"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="78"/>
       <c r="D22" s="24" t="s">
         <v>50</v>
       </c>
@@ -2994,20 +2994,20 @@
       <c r="F22" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G22" s="56"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="83"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="22"/>
       <c r="N22" s="23"/>
-      <c r="O22" s="47"/>
+      <c r="O22" s="83"/>
     </row>
     <row r="23" spans="1:15" ht="15.4">
-      <c r="A23" s="56"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="24" t="s">
         <v>52</v>
       </c>
@@ -3017,20 +3017,20 @@
       <c r="F23" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G23" s="56"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="M23" s="27"/>
       <c r="N23" s="23"/>
-      <c r="O23" s="47"/>
+      <c r="O23" s="83"/>
     </row>
     <row r="24" spans="1:15" ht="15.4">
-      <c r="A24" s="56"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="59"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="78"/>
       <c r="D24" s="24" t="s">
         <v>53</v>
       </c>
@@ -3040,22 +3040,22 @@
       <c r="F24" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G24" s="56"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
       <c r="M24" s="22"/>
       <c r="N24" s="23"/>
-      <c r="O24" s="47"/>
+      <c r="O24" s="83"/>
     </row>
     <row r="25" spans="1:15" ht="15.4">
-      <c r="A25" s="56"/>
-      <c r="B25" s="61" t="s">
+      <c r="A25" s="75"/>
+      <c r="B25" s="80" t="s">
         <v>256</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="81" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="29" t="s">
@@ -3067,21 +3067,21 @@
       <c r="F25" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G25" s="65" t="s">
+      <c r="G25" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="48"/>
-      <c r="J25" s="49"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="85"/>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="22"/>
       <c r="N25" s="23"/>
-      <c r="O25" s="46"/>
+      <c r="O25" s="82"/>
     </row>
     <row r="26" spans="1:15" ht="15.4">
-      <c r="A26" s="56"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="64"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="24" t="s">
         <v>57</v>
       </c>
@@ -3091,19 +3091,19 @@
       <c r="F26" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G26" s="62"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="50"/>
+      <c r="G26" s="47"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="86"/>
       <c r="K26" s="26"/>
       <c r="L26" s="26"/>
       <c r="M26" s="22"/>
       <c r="N26" s="23"/>
-      <c r="O26" s="47"/>
+      <c r="O26" s="83"/>
     </row>
     <row r="27" spans="1:15" ht="15.4">
-      <c r="A27" s="56"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="64"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="24" t="s">
         <v>58</v>
       </c>
@@ -3113,19 +3113,19 @@
       <c r="F27" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="50"/>
+      <c r="G27" s="47"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="86"/>
       <c r="K27" s="26"/>
       <c r="L27" s="26"/>
       <c r="M27" s="22"/>
       <c r="N27" s="23"/>
-      <c r="O27" s="47"/>
+      <c r="O27" s="83"/>
     </row>
     <row r="28" spans="1:15" ht="15.4">
-      <c r="A28" s="56"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="64"/>
+      <c r="A28" s="75"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="65"/>
       <c r="D28" s="24" t="s">
         <v>59</v>
       </c>
@@ -3135,19 +3135,19 @@
       <c r="F28" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="50"/>
+      <c r="G28" s="47"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="86"/>
       <c r="K28" s="26"/>
       <c r="L28" s="26"/>
       <c r="M28" s="22"/>
       <c r="N28" s="23"/>
-      <c r="O28" s="47"/>
+      <c r="O28" s="83"/>
     </row>
     <row r="29" spans="1:15" ht="15.4">
-      <c r="A29" s="56"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="64"/>
+      <c r="A29" s="75"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="65"/>
       <c r="D29" s="24" t="s">
         <v>60</v>
       </c>
@@ -3157,19 +3157,19 @@
       <c r="F29" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="50"/>
+      <c r="G29" s="47"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="86"/>
       <c r="K29" s="26"/>
       <c r="L29" s="26"/>
       <c r="M29" s="27"/>
       <c r="N29" s="23"/>
-      <c r="O29" s="47"/>
+      <c r="O29" s="83"/>
     </row>
     <row r="30" spans="1:15" ht="15.4">
-      <c r="A30" s="56"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="64"/>
+      <c r="A30" s="75"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="65"/>
       <c r="D30" s="24" t="s">
         <v>61</v>
       </c>
@@ -3179,21 +3179,21 @@
       <c r="F30" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="50"/>
+      <c r="G30" s="47"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="86"/>
       <c r="K30" s="26"/>
       <c r="L30" s="26"/>
       <c r="M30" s="27"/>
       <c r="N30" s="23"/>
-      <c r="O30" s="47"/>
+      <c r="O30" s="83"/>
     </row>
     <row r="31" spans="1:15" ht="15.4">
-      <c r="A31" s="56"/>
-      <c r="B31" s="62" t="s">
+      <c r="A31" s="75"/>
+      <c r="B31" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="81" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="29" t="s">
@@ -3205,21 +3205,21 @@
       <c r="F31" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G31" s="65" t="s">
+      <c r="G31" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="51"/>
-      <c r="J31" s="49"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="85"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="27"/>
       <c r="N31" s="31"/>
-      <c r="O31" s="52"/>
+      <c r="O31" s="88"/>
     </row>
     <row r="32" spans="1:15" ht="15.4">
-      <c r="A32" s="56"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="64"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="65"/>
       <c r="D32" s="24" t="s">
         <v>65</v>
       </c>
@@ -3229,19 +3229,19 @@
       <c r="F32" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G32" s="62"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
       <c r="K32" s="26"/>
       <c r="L32" s="26"/>
       <c r="M32" s="27"/>
       <c r="N32" s="31"/>
-      <c r="O32" s="47"/>
+      <c r="O32" s="83"/>
     </row>
     <row r="33" spans="1:15" ht="15.4">
-      <c r="A33" s="56"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="64"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="65"/>
       <c r="D33" s="24" t="s">
         <v>66</v>
       </c>
@@ -3251,19 +3251,19 @@
       <c r="F33" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G33" s="62"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="83"/>
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="27"/>
       <c r="N33" s="31"/>
-      <c r="O33" s="47"/>
+      <c r="O33" s="83"/>
     </row>
     <row r="34" spans="1:15" ht="15.4">
-      <c r="A34" s="56"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="64"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="65"/>
       <c r="D34" s="24" t="s">
         <v>67</v>
       </c>
@@ -3273,19 +3273,19 @@
       <c r="F34" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G34" s="62"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="83"/>
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
       <c r="M34" s="27"/>
       <c r="N34" s="31"/>
-      <c r="O34" s="47"/>
+      <c r="O34" s="83"/>
     </row>
     <row r="35" spans="1:15" ht="15.4">
-      <c r="A35" s="56"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="64"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="65"/>
       <c r="D35" s="24" t="s">
         <v>68</v>
       </c>
@@ -3295,23 +3295,23 @@
       <c r="F35" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G35" s="62"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
       <c r="K35" s="26"/>
       <c r="L35" s="26"/>
       <c r="M35" s="27"/>
       <c r="N35" s="31"/>
-      <c r="O35" s="47"/>
+      <c r="O35" s="83"/>
     </row>
     <row r="36" spans="1:15" ht="15.4">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="64" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="33" t="s">
@@ -3323,14 +3323,14 @@
       <c r="F36" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G36" s="65" t="s">
+      <c r="G36" s="66" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15.4">
-      <c r="A37" s="62"/>
-      <c r="B37" s="62"/>
-      <c r="C37" s="64"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="65"/>
       <c r="D37" s="33" t="s">
         <v>74</v>
       </c>
@@ -3340,12 +3340,12 @@
       <c r="F37" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G37" s="62"/>
+      <c r="G37" s="47"/>
     </row>
     <row r="38" spans="1:15" ht="15.4">
-      <c r="A38" s="62"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="64"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="65"/>
       <c r="D38" s="33" t="s">
         <v>76</v>
       </c>
@@ -3355,12 +3355,12 @@
       <c r="F38" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G38" s="62"/>
+      <c r="G38" s="47"/>
     </row>
     <row r="39" spans="1:15" ht="15.4">
-      <c r="A39" s="62"/>
-      <c r="B39" s="62"/>
-      <c r="C39" s="64"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="65"/>
       <c r="D39" s="33" t="s">
         <v>78</v>
       </c>
@@ -3370,12 +3370,12 @@
       <c r="F39" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G39" s="62"/>
+      <c r="G39" s="47"/>
     </row>
     <row r="40" spans="1:15" ht="15.4">
-      <c r="A40" s="62"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="64"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="65"/>
       <c r="D40" s="33" t="s">
         <v>79</v>
       </c>
@@ -3385,12 +3385,12 @@
       <c r="F40" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G40" s="62"/>
+      <c r="G40" s="47"/>
     </row>
     <row r="41" spans="1:15" ht="15.4">
-      <c r="A41" s="62"/>
-      <c r="B41" s="62"/>
-      <c r="C41" s="64"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="65"/>
       <c r="D41" s="33" t="s">
         <v>81</v>
       </c>
@@ -3400,12 +3400,12 @@
       <c r="F41" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G41" s="62"/>
+      <c r="G41" s="47"/>
     </row>
     <row r="42" spans="1:15" ht="15.4">
-      <c r="A42" s="62"/>
-      <c r="B42" s="62"/>
-      <c r="C42" s="64"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="65"/>
       <c r="D42" s="33" t="s">
         <v>82</v>
       </c>
@@ -3415,12 +3415,12 @@
       <c r="F42" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G42" s="62"/>
+      <c r="G42" s="47"/>
     </row>
     <row r="43" spans="1:15" ht="15.4">
-      <c r="A43" s="62"/>
-      <c r="B43" s="62"/>
-      <c r="C43" s="64"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="65"/>
       <c r="D43" s="33" t="s">
         <v>84</v>
       </c>
@@ -3430,12 +3430,12 @@
       <c r="F43" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G43" s="62"/>
+      <c r="G43" s="47"/>
     </row>
     <row r="44" spans="1:15" ht="15.4">
-      <c r="A44" s="62"/>
-      <c r="B44" s="62"/>
-      <c r="C44" s="64"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="65"/>
       <c r="D44" s="33" t="s">
         <v>86</v>
       </c>
@@ -3445,14 +3445,14 @@
       <c r="F44" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G44" s="62"/>
+      <c r="G44" s="47"/>
     </row>
     <row r="45" spans="1:15" ht="15.4">
-      <c r="A45" s="62"/>
-      <c r="B45" s="69" t="s">
+      <c r="A45" s="47"/>
+      <c r="B45" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -3464,14 +3464,14 @@
       <c r="F45" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G45" s="65" t="s">
+      <c r="G45" s="66" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.4">
-      <c r="A46" s="62"/>
-      <c r="B46" s="62"/>
-      <c r="C46" s="64"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="65"/>
       <c r="D46" s="33" t="s">
         <v>93</v>
       </c>
@@ -3481,12 +3481,12 @@
       <c r="F46" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G46" s="62"/>
+      <c r="G46" s="47"/>
     </row>
     <row r="47" spans="1:15" ht="15.4">
-      <c r="A47" s="62"/>
-      <c r="B47" s="62"/>
-      <c r="C47" s="64"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="65"/>
       <c r="D47" s="33" t="s">
         <v>95</v>
       </c>
@@ -3496,12 +3496,12 @@
       <c r="F47" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G47" s="62"/>
+      <c r="G47" s="47"/>
     </row>
     <row r="48" spans="1:15" ht="15.4">
-      <c r="A48" s="62"/>
-      <c r="B48" s="62"/>
-      <c r="C48" s="64"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="65"/>
       <c r="D48" s="33" t="s">
         <v>97</v>
       </c>
@@ -3511,10 +3511,10 @@
       <c r="F48" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G48" s="62"/>
+      <c r="G48" s="47"/>
     </row>
     <row r="49" spans="1:7" ht="25.5">
-      <c r="A49" s="66" t="s">
+      <c r="A49" s="61" t="s">
         <v>98</v>
       </c>
       <c r="B49" s="33" t="s">
@@ -3537,11 +3537,11 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.4">
-      <c r="A50" s="62"/>
-      <c r="B50" s="69" t="s">
+      <c r="A50" s="47"/>
+      <c r="B50" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="64" t="s">
         <v>54</v>
       </c>
       <c r="D50" s="33" t="s">
@@ -3553,14 +3553,14 @@
       <c r="F50" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G50" s="65" t="s">
+      <c r="G50" s="66" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.4">
-      <c r="A51" s="62"/>
-      <c r="B51" s="62"/>
-      <c r="C51" s="64"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="65"/>
       <c r="D51" s="33" t="s">
         <v>106</v>
       </c>
@@ -3570,12 +3570,12 @@
       <c r="F51" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G51" s="62"/>
+      <c r="G51" s="47"/>
     </row>
     <row r="52" spans="1:7" ht="15.4">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
-      <c r="C52" s="64"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="65"/>
       <c r="D52" s="33" t="s">
         <v>108</v>
       </c>
@@ -3585,12 +3585,12 @@
       <c r="F52" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G52" s="62"/>
+      <c r="G52" s="47"/>
     </row>
     <row r="53" spans="1:7" ht="15.4">
-      <c r="A53" s="62"/>
-      <c r="B53" s="62"/>
-      <c r="C53" s="64"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="65"/>
       <c r="D53" s="33" t="s">
         <v>110</v>
       </c>
@@ -3600,12 +3600,12 @@
       <c r="F53" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G53" s="62"/>
+      <c r="G53" s="47"/>
     </row>
     <row r="54" spans="1:7" ht="15.4">
-      <c r="A54" s="62"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="64"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="65"/>
       <c r="D54" s="33" t="s">
         <v>112</v>
       </c>
@@ -3615,12 +3615,12 @@
       <c r="F54" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G54" s="62"/>
+      <c r="G54" s="47"/>
     </row>
     <row r="55" spans="1:7" ht="15.4">
-      <c r="A55" s="62"/>
-      <c r="B55" s="62"/>
-      <c r="C55" s="64"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="65"/>
       <c r="D55" s="33" t="s">
         <v>114</v>
       </c>
@@ -3630,12 +3630,12 @@
       <c r="F55" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G55" s="62"/>
+      <c r="G55" s="47"/>
     </row>
     <row r="56" spans="1:7" ht="15.4">
-      <c r="A56" s="62"/>
-      <c r="B56" s="62"/>
-      <c r="C56" s="64"/>
+      <c r="A56" s="47"/>
+      <c r="B56" s="47"/>
+      <c r="C56" s="65"/>
       <c r="D56" s="33" t="s">
         <v>115</v>
       </c>
@@ -3645,12 +3645,12 @@
       <c r="F56" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G56" s="62"/>
+      <c r="G56" s="47"/>
     </row>
     <row r="57" spans="1:7" ht="15.4">
-      <c r="A57" s="62"/>
-      <c r="B57" s="62"/>
-      <c r="C57" s="64"/>
+      <c r="A57" s="47"/>
+      <c r="B57" s="47"/>
+      <c r="C57" s="65"/>
       <c r="D57" s="33" t="s">
         <v>116</v>
       </c>
@@ -3660,12 +3660,12 @@
       <c r="F57" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G57" s="62"/>
+      <c r="G57" s="47"/>
     </row>
     <row r="58" spans="1:7" ht="15.4">
-      <c r="A58" s="62"/>
-      <c r="B58" s="62"/>
-      <c r="C58" s="64"/>
+      <c r="A58" s="47"/>
+      <c r="B58" s="47"/>
+      <c r="C58" s="65"/>
       <c r="D58" s="33" t="s">
         <v>117</v>
       </c>
@@ -3675,12 +3675,12 @@
       <c r="F58" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G58" s="62"/>
+      <c r="G58" s="47"/>
     </row>
     <row r="59" spans="1:7" ht="15.4">
-      <c r="A59" s="62"/>
-      <c r="B59" s="62"/>
-      <c r="C59" s="64"/>
+      <c r="A59" s="47"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="65"/>
       <c r="D59" s="33" t="s">
         <v>118</v>
       </c>
@@ -3690,10 +3690,10 @@
       <c r="F59" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G59" s="62"/>
+      <c r="G59" s="47"/>
     </row>
     <row r="60" spans="1:7" ht="25.5">
-      <c r="A60" s="62"/>
+      <c r="A60" s="47"/>
       <c r="B60" s="33" t="s">
         <v>119</v>
       </c>
@@ -3714,11 +3714,11 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.4">
-      <c r="A61" s="62"/>
-      <c r="B61" s="69" t="s">
+      <c r="A61" s="47"/>
+      <c r="B61" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="68" t="s">
+      <c r="C61" s="64" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="33" t="s">
@@ -3730,14 +3730,14 @@
       <c r="F61" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G61" s="65" t="s">
+      <c r="G61" s="66" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.4">
-      <c r="A62" s="62"/>
-      <c r="B62" s="62"/>
-      <c r="C62" s="64"/>
+      <c r="A62" s="47"/>
+      <c r="B62" s="47"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="33" t="s">
         <v>127</v>
       </c>
@@ -3747,12 +3747,12 @@
       <c r="F62" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G62" s="62"/>
+      <c r="G62" s="47"/>
     </row>
     <row r="63" spans="1:7" ht="25.5">
-      <c r="A63" s="62"/>
-      <c r="B63" s="62"/>
-      <c r="C63" s="64"/>
+      <c r="A63" s="47"/>
+      <c r="B63" s="47"/>
+      <c r="C63" s="65"/>
       <c r="D63" s="33" t="s">
         <v>129</v>
       </c>
@@ -3762,12 +3762,12 @@
       <c r="F63" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G63" s="62"/>
+      <c r="G63" s="47"/>
     </row>
     <row r="64" spans="1:7" ht="15.4">
-      <c r="A64" s="62"/>
-      <c r="B64" s="62"/>
-      <c r="C64" s="64"/>
+      <c r="A64" s="47"/>
+      <c r="B64" s="47"/>
+      <c r="C64" s="65"/>
       <c r="D64" s="33" t="s">
         <v>131</v>
       </c>
@@ -3777,12 +3777,12 @@
       <c r="F64" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G64" s="62"/>
+      <c r="G64" s="47"/>
     </row>
     <row r="65" spans="1:7" ht="25.5">
-      <c r="A65" s="62"/>
-      <c r="B65" s="62"/>
-      <c r="C65" s="64"/>
+      <c r="A65" s="47"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="65"/>
       <c r="D65" s="33" t="s">
         <v>133</v>
       </c>
@@ -3792,12 +3792,12 @@
       <c r="F65" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G65" s="62"/>
+      <c r="G65" s="47"/>
     </row>
     <row r="66" spans="1:7" ht="25.5">
-      <c r="A66" s="62"/>
-      <c r="B66" s="62"/>
-      <c r="C66" s="64"/>
+      <c r="A66" s="47"/>
+      <c r="B66" s="47"/>
+      <c r="C66" s="65"/>
       <c r="D66" s="33" t="s">
         <v>135</v>
       </c>
@@ -3807,14 +3807,14 @@
       <c r="F66" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G66" s="62"/>
+      <c r="G66" s="47"/>
     </row>
     <row r="67" spans="1:7" ht="15.4">
-      <c r="A67" s="62"/>
-      <c r="B67" s="69" t="s">
+      <c r="A67" s="47"/>
+      <c r="B67" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="64" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="33" t="s">
@@ -3826,14 +3826,14 @@
       <c r="F67" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G67" s="65" t="s">
+      <c r="G67" s="66" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.4">
-      <c r="A68" s="62"/>
-      <c r="B68" s="62"/>
-      <c r="C68" s="64"/>
+      <c r="A68" s="47"/>
+      <c r="B68" s="47"/>
+      <c r="C68" s="65"/>
       <c r="D68" s="33" t="s">
         <v>141</v>
       </c>
@@ -3843,12 +3843,12 @@
       <c r="F68" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G68" s="62"/>
+      <c r="G68" s="47"/>
     </row>
     <row r="69" spans="1:7" ht="15.4">
-      <c r="A69" s="62"/>
-      <c r="B69" s="62"/>
-      <c r="C69" s="64"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="65"/>
       <c r="D69" s="33" t="s">
         <v>143</v>
       </c>
@@ -3858,12 +3858,12 @@
       <c r="F69" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G69" s="62"/>
+      <c r="G69" s="47"/>
     </row>
     <row r="70" spans="1:7" ht="25.5">
-      <c r="A70" s="62"/>
-      <c r="B70" s="62"/>
-      <c r="C70" s="64"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="33" t="s">
         <v>145</v>
       </c>
@@ -3873,14 +3873,14 @@
       <c r="F70" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G70" s="62"/>
+      <c r="G70" s="47"/>
     </row>
     <row r="71" spans="1:7" ht="15.4">
-      <c r="A71" s="62"/>
-      <c r="B71" s="69" t="s">
+      <c r="A71" s="47"/>
+      <c r="B71" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="68" t="s">
+      <c r="C71" s="64" t="s">
         <v>54</v>
       </c>
       <c r="D71" s="33" t="s">
@@ -3892,14 +3892,14 @@
       <c r="F71" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G71" s="65" t="s">
+      <c r="G71" s="66" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.4">
-      <c r="A72" s="62"/>
-      <c r="B72" s="62"/>
-      <c r="C72" s="64"/>
+      <c r="A72" s="47"/>
+      <c r="B72" s="47"/>
+      <c r="C72" s="65"/>
       <c r="D72" s="33" t="s">
         <v>151</v>
       </c>
@@ -3909,12 +3909,12 @@
       <c r="F72" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G72" s="62"/>
+      <c r="G72" s="47"/>
     </row>
     <row r="73" spans="1:7" ht="15.4">
-      <c r="A73" s="62"/>
-      <c r="B73" s="62"/>
-      <c r="C73" s="64"/>
+      <c r="A73" s="47"/>
+      <c r="B73" s="47"/>
+      <c r="C73" s="65"/>
       <c r="D73" s="33" t="s">
         <v>153</v>
       </c>
@@ -3924,12 +3924,12 @@
       <c r="F73" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G73" s="62"/>
+      <c r="G73" s="47"/>
     </row>
     <row r="74" spans="1:7" ht="25.5">
-      <c r="A74" s="62"/>
-      <c r="B74" s="62"/>
-      <c r="C74" s="64"/>
+      <c r="A74" s="47"/>
+      <c r="B74" s="47"/>
+      <c r="C74" s="65"/>
       <c r="D74" s="33" t="s">
         <v>155</v>
       </c>
@@ -3939,12 +3939,12 @@
       <c r="F74" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G74" s="62"/>
+      <c r="G74" s="47"/>
     </row>
     <row r="75" spans="1:7" ht="25.5">
-      <c r="A75" s="62"/>
-      <c r="B75" s="62"/>
-      <c r="C75" s="64"/>
+      <c r="A75" s="47"/>
+      <c r="B75" s="47"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="33" t="s">
         <v>157</v>
       </c>
@@ -3954,14 +3954,14 @@
       <c r="F75" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G75" s="62"/>
+      <c r="G75" s="47"/>
     </row>
     <row r="76" spans="1:7" ht="25.5">
-      <c r="A76" s="62"/>
+      <c r="A76" s="47"/>
       <c r="B76" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="68" t="s">
+      <c r="C76" s="64" t="s">
         <v>32</v>
       </c>
       <c r="D76" s="33" t="s">
@@ -3973,14 +3973,14 @@
       <c r="F76" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G76" s="65" t="s">
+      <c r="G76" s="66" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.4">
-      <c r="A77" s="62"/>
-      <c r="B77" s="62"/>
-      <c r="C77" s="64"/>
+      <c r="A77" s="47"/>
+      <c r="B77" s="47"/>
+      <c r="C77" s="65"/>
       <c r="D77" s="33" t="s">
         <v>162</v>
       </c>
@@ -3990,12 +3990,12 @@
       <c r="F77" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G77" s="62"/>
+      <c r="G77" s="47"/>
     </row>
     <row r="78" spans="1:7" ht="38.25">
-      <c r="A78" s="62"/>
-      <c r="B78" s="62"/>
-      <c r="C78" s="64"/>
+      <c r="A78" s="47"/>
+      <c r="B78" s="47"/>
+      <c r="C78" s="65"/>
       <c r="D78" s="33" t="s">
         <v>164</v>
       </c>
@@ -4005,12 +4005,12 @@
       <c r="F78" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G78" s="62"/>
+      <c r="G78" s="47"/>
     </row>
     <row r="79" spans="1:7" ht="38.25">
-      <c r="A79" s="62"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="64"/>
+      <c r="A79" s="47"/>
+      <c r="B79" s="47"/>
+      <c r="C79" s="65"/>
       <c r="D79" s="33" t="s">
         <v>166</v>
       </c>
@@ -4020,12 +4020,12 @@
       <c r="F79" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G79" s="62"/>
+      <c r="G79" s="47"/>
     </row>
     <row r="80" spans="1:7" ht="15.4">
-      <c r="A80" s="62"/>
-      <c r="B80" s="62"/>
-      <c r="C80" s="64"/>
+      <c r="A80" s="47"/>
+      <c r="B80" s="47"/>
+      <c r="C80" s="65"/>
       <c r="D80" s="33" t="s">
         <v>167</v>
       </c>
@@ -4035,10 +4035,10 @@
       <c r="F80" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G80" s="62"/>
+      <c r="G80" s="47"/>
     </row>
     <row r="81" spans="1:7" ht="25.5">
-      <c r="A81" s="66" t="s">
+      <c r="A81" s="61" t="s">
         <v>283</v>
       </c>
       <c r="B81" s="33" t="s">
@@ -4061,11 +4061,11 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.4">
-      <c r="A82" s="62"/>
-      <c r="B82" s="69" t="s">
+      <c r="A82" s="47"/>
+      <c r="B82" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="64" t="s">
         <v>54</v>
       </c>
       <c r="D82" s="33" t="s">
@@ -4077,14 +4077,14 @@
       <c r="F82" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G82" s="65" t="s">
+      <c r="G82" s="66" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.4">
-      <c r="A83" s="62"/>
-      <c r="B83" s="62"/>
-      <c r="C83" s="64"/>
+      <c r="A83" s="47"/>
+      <c r="B83" s="47"/>
+      <c r="C83" s="65"/>
       <c r="D83" s="33" t="s">
         <v>177</v>
       </c>
@@ -4094,12 +4094,12 @@
       <c r="F83" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G83" s="62"/>
+      <c r="G83" s="47"/>
     </row>
     <row r="84" spans="1:7" ht="15.4">
-      <c r="A84" s="62"/>
-      <c r="B84" s="62"/>
-      <c r="C84" s="64"/>
+      <c r="A84" s="47"/>
+      <c r="B84" s="47"/>
+      <c r="C84" s="65"/>
       <c r="D84" s="33" t="s">
         <v>179</v>
       </c>
@@ -4109,12 +4109,12 @@
       <c r="F84" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G84" s="62"/>
+      <c r="G84" s="47"/>
     </row>
     <row r="85" spans="1:7" ht="15.4">
-      <c r="A85" s="62"/>
-      <c r="B85" s="62"/>
-      <c r="C85" s="64"/>
+      <c r="A85" s="47"/>
+      <c r="B85" s="47"/>
+      <c r="C85" s="65"/>
       <c r="D85" s="33" t="s">
         <v>180</v>
       </c>
@@ -4124,14 +4124,14 @@
       <c r="F85" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G85" s="62"/>
+      <c r="G85" s="47"/>
     </row>
     <row r="86" spans="1:7" ht="15.4">
-      <c r="A86" s="62"/>
-      <c r="B86" s="69" t="s">
+      <c r="A86" s="47"/>
+      <c r="B86" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="C86" s="68" t="s">
+      <c r="C86" s="64" t="s">
         <v>62</v>
       </c>
       <c r="D86" s="33" t="s">
@@ -4143,14 +4143,14 @@
       <c r="F86" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G86" s="65" t="s">
+      <c r="G86" s="66" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="25.5">
-      <c r="A87" s="62"/>
-      <c r="B87" s="62"/>
-      <c r="C87" s="64"/>
+      <c r="A87" s="47"/>
+      <c r="B87" s="47"/>
+      <c r="C87" s="65"/>
       <c r="D87" s="33" t="s">
         <v>184</v>
       </c>
@@ -4160,12 +4160,12 @@
       <c r="F87" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G87" s="62"/>
+      <c r="G87" s="47"/>
     </row>
     <row r="88" spans="1:7" ht="25.5">
-      <c r="A88" s="62"/>
-      <c r="B88" s="62"/>
-      <c r="C88" s="64"/>
+      <c r="A88" s="47"/>
+      <c r="B88" s="47"/>
+      <c r="C88" s="65"/>
       <c r="D88" s="33" t="s">
         <v>186</v>
       </c>
@@ -4175,14 +4175,14 @@
       <c r="F88" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G88" s="62"/>
+      <c r="G88" s="47"/>
     </row>
     <row r="89" spans="1:7" ht="25.5">
-      <c r="A89" s="62"/>
-      <c r="B89" s="69" t="s">
+      <c r="A89" s="47"/>
+      <c r="B89" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="C89" s="68" t="s">
+      <c r="C89" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D89" s="33" t="s">
@@ -4194,14 +4194,14 @@
       <c r="F89" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G89" s="71" t="s">
+      <c r="G89" s="68" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.4">
-      <c r="A90" s="62"/>
-      <c r="B90" s="62"/>
-      <c r="C90" s="64"/>
+      <c r="A90" s="47"/>
+      <c r="B90" s="47"/>
+      <c r="C90" s="65"/>
       <c r="D90" s="33" t="s">
         <v>191</v>
       </c>
@@ -4211,14 +4211,14 @@
       <c r="F90" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G90" s="72"/>
+      <c r="G90" s="62"/>
     </row>
     <row r="91" spans="1:7" ht="15.4">
-      <c r="A91" s="62"/>
-      <c r="B91" s="73" t="s">
+      <c r="A91" s="47"/>
+      <c r="B91" s="69" t="s">
         <v>193</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="64" t="s">
         <v>32</v>
       </c>
       <c r="D91" s="33" t="s">
@@ -4230,14 +4230,14 @@
       <c r="F91" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G91" s="65" t="s">
+      <c r="G91" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.4">
-      <c r="A92" s="62"/>
-      <c r="B92" s="62"/>
-      <c r="C92" s="64"/>
+      <c r="A92" s="47"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="65"/>
       <c r="D92" s="33" t="s">
         <v>196</v>
       </c>
@@ -4247,12 +4247,12 @@
       <c r="F92" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G92" s="62"/>
+      <c r="G92" s="47"/>
     </row>
     <row r="93" spans="1:7" ht="15.4">
-      <c r="A93" s="62"/>
-      <c r="B93" s="62"/>
-      <c r="C93" s="64"/>
+      <c r="A93" s="47"/>
+      <c r="B93" s="47"/>
+      <c r="C93" s="65"/>
       <c r="D93" s="33" t="s">
         <v>198</v>
       </c>
@@ -4262,12 +4262,12 @@
       <c r="F93" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G93" s="62"/>
+      <c r="G93" s="47"/>
     </row>
     <row r="94" spans="1:7" ht="15.4">
-      <c r="A94" s="62"/>
-      <c r="B94" s="62"/>
-      <c r="C94" s="64"/>
+      <c r="A94" s="47"/>
+      <c r="B94" s="47"/>
+      <c r="C94" s="65"/>
       <c r="D94" s="33" t="s">
         <v>200</v>
       </c>
@@ -4277,12 +4277,12 @@
       <c r="F94" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G94" s="62"/>
+      <c r="G94" s="47"/>
     </row>
     <row r="95" spans="1:7" ht="15.4">
-      <c r="A95" s="62"/>
-      <c r="B95" s="62"/>
-      <c r="C95" s="64"/>
+      <c r="A95" s="47"/>
+      <c r="B95" s="47"/>
+      <c r="C95" s="65"/>
       <c r="D95" s="33" t="s">
         <v>201</v>
       </c>
@@ -4292,14 +4292,14 @@
       <c r="F95" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G95" s="62"/>
+      <c r="G95" s="47"/>
     </row>
     <row r="96" spans="1:7" ht="15.4">
-      <c r="A96" s="62"/>
-      <c r="B96" s="69" t="s">
+      <c r="A96" s="47"/>
+      <c r="B96" s="63" t="s">
         <v>203</v>
       </c>
-      <c r="C96" s="68" t="s">
+      <c r="C96" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D96" s="33" t="s">
@@ -4311,14 +4311,14 @@
       <c r="F96" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G96" s="65" t="s">
+      <c r="G96" s="66" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15.4">
-      <c r="A97" s="62"/>
-      <c r="B97" s="62"/>
-      <c r="C97" s="64"/>
+      <c r="A97" s="47"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="65"/>
       <c r="D97" s="33" t="s">
         <v>206</v>
       </c>
@@ -4328,16 +4328,16 @@
       <c r="F97" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G97" s="62"/>
+      <c r="G97" s="47"/>
     </row>
     <row r="98" spans="1:7" ht="15.4">
-      <c r="A98" s="66" t="s">
+      <c r="A98" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="B98" s="69" t="s">
+      <c r="B98" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="C98" s="68" t="s">
+      <c r="C98" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D98" s="33" t="s">
@@ -4349,14 +4349,14 @@
       <c r="F98" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G98" s="65" t="s">
+      <c r="G98" s="66" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15.4">
-      <c r="A99" s="62"/>
-      <c r="B99" s="62"/>
-      <c r="C99" s="64"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="65"/>
       <c r="D99" s="33" t="s">
         <v>212</v>
       </c>
@@ -4366,14 +4366,14 @@
       <c r="F99" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G99" s="62"/>
+      <c r="G99" s="47"/>
     </row>
     <row r="100" spans="1:7" ht="15.4">
-      <c r="A100" s="62"/>
-      <c r="B100" s="69" t="s">
+      <c r="A100" s="47"/>
+      <c r="B100" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="C100" s="68" t="s">
+      <c r="C100" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="33" t="s">
@@ -4385,12 +4385,12 @@
       <c r="F100" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G100" s="62"/>
+      <c r="G100" s="47"/>
     </row>
     <row r="101" spans="1:7" ht="15.4">
-      <c r="A101" s="62"/>
-      <c r="B101" s="62"/>
-      <c r="C101" s="64"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="65"/>
       <c r="D101" s="33" t="s">
         <v>216</v>
       </c>
@@ -4400,14 +4400,14 @@
       <c r="F101" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G101" s="62"/>
+      <c r="G101" s="47"/>
     </row>
     <row r="102" spans="1:7" ht="25.5">
-      <c r="A102" s="62"/>
-      <c r="B102" s="69" t="s">
+      <c r="A102" s="47"/>
+      <c r="B102" s="63" t="s">
         <v>217</v>
       </c>
-      <c r="C102" s="68" t="s">
+      <c r="C102" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D102" s="33" t="s">
@@ -4419,12 +4419,12 @@
       <c r="F102" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G102" s="62"/>
+      <c r="G102" s="47"/>
     </row>
     <row r="103" spans="1:7" ht="25.5">
-      <c r="A103" s="62"/>
-      <c r="B103" s="62"/>
-      <c r="C103" s="64"/>
+      <c r="A103" s="47"/>
+      <c r="B103" s="47"/>
+      <c r="C103" s="65"/>
       <c r="D103" s="33" t="s">
         <v>219</v>
       </c>
@@ -4434,12 +4434,12 @@
       <c r="F103" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G103" s="62"/>
+      <c r="G103" s="47"/>
     </row>
     <row r="104" spans="1:7" ht="15.4">
-      <c r="A104" s="62"/>
-      <c r="B104" s="62"/>
-      <c r="C104" s="64"/>
+      <c r="A104" s="47"/>
+      <c r="B104" s="47"/>
+      <c r="C104" s="65"/>
       <c r="D104" s="33" t="s">
         <v>221</v>
       </c>
@@ -4449,12 +4449,12 @@
       <c r="F104" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G104" s="62"/>
+      <c r="G104" s="47"/>
     </row>
     <row r="105" spans="1:7" ht="25.5">
-      <c r="A105" s="62"/>
-      <c r="B105" s="62"/>
-      <c r="C105" s="64"/>
+      <c r="A105" s="47"/>
+      <c r="B105" s="47"/>
+      <c r="C105" s="65"/>
       <c r="D105" s="33" t="s">
         <v>222</v>
       </c>
@@ -4464,12 +4464,12 @@
       <c r="F105" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G105" s="62"/>
+      <c r="G105" s="47"/>
     </row>
     <row r="106" spans="1:7" ht="25.5">
-      <c r="A106" s="62"/>
-      <c r="B106" s="62"/>
-      <c r="C106" s="64"/>
+      <c r="A106" s="47"/>
+      <c r="B106" s="47"/>
+      <c r="C106" s="65"/>
       <c r="D106" s="33" t="s">
         <v>223</v>
       </c>
@@ -4479,12 +4479,12 @@
       <c r="F106" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G106" s="62"/>
+      <c r="G106" s="47"/>
     </row>
     <row r="107" spans="1:7" ht="15.4">
-      <c r="A107" s="62"/>
-      <c r="B107" s="62"/>
-      <c r="C107" s="64"/>
+      <c r="A107" s="47"/>
+      <c r="B107" s="47"/>
+      <c r="C107" s="65"/>
       <c r="D107" s="33" t="s">
         <v>224</v>
       </c>
@@ -4494,16 +4494,16 @@
       <c r="F107" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G107" s="62"/>
+      <c r="G107" s="47"/>
     </row>
     <row r="108" spans="1:7" ht="15.4">
-      <c r="A108" s="66" t="s">
+      <c r="A108" s="61" t="s">
         <v>225</v>
       </c>
-      <c r="B108" s="69" t="s">
+      <c r="B108" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="C108" s="68" t="s">
+      <c r="C108" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D108" s="33" t="s">
@@ -4515,14 +4515,14 @@
       <c r="F108" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G108" s="65" t="s">
+      <c r="G108" s="66" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15.4">
-      <c r="A109" s="62"/>
-      <c r="B109" s="62"/>
-      <c r="C109" s="64"/>
+      <c r="A109" s="47"/>
+      <c r="B109" s="47"/>
+      <c r="C109" s="65"/>
       <c r="D109" s="33" t="s">
         <v>229</v>
       </c>
@@ -4532,14 +4532,14 @@
       <c r="F109" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G109" s="62"/>
+      <c r="G109" s="47"/>
     </row>
     <row r="110" spans="1:7" ht="25.5">
-      <c r="A110" s="62"/>
-      <c r="B110" s="69" t="s">
+      <c r="A110" s="47"/>
+      <c r="B110" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="C110" s="68" t="s">
+      <c r="C110" s="64" t="s">
         <v>54</v>
       </c>
       <c r="D110" s="33" t="s">
@@ -4551,12 +4551,12 @@
       <c r="F110" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G110" s="62"/>
+      <c r="G110" s="47"/>
     </row>
     <row r="111" spans="1:7" ht="15.4">
-      <c r="A111" s="62"/>
-      <c r="B111" s="62"/>
-      <c r="C111" s="64"/>
+      <c r="A111" s="47"/>
+      <c r="B111" s="47"/>
+      <c r="C111" s="65"/>
       <c r="D111" s="33" t="s">
         <v>233</v>
       </c>
@@ -4566,14 +4566,14 @@
       <c r="F111" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G111" s="62"/>
+      <c r="G111" s="47"/>
     </row>
     <row r="112" spans="1:7" ht="15.4">
-      <c r="A112" s="62"/>
-      <c r="B112" s="69" t="s">
+      <c r="A112" s="47"/>
+      <c r="B112" s="63" t="s">
         <v>235</v>
       </c>
-      <c r="C112" s="68" t="s">
+      <c r="C112" s="64" t="s">
         <v>89</v>
       </c>
       <c r="D112" s="33" t="s">
@@ -4585,12 +4585,12 @@
       <c r="F112" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G112" s="62"/>
+      <c r="G112" s="47"/>
     </row>
     <row r="113" spans="1:7" ht="15.4">
-      <c r="A113" s="62"/>
-      <c r="B113" s="62"/>
-      <c r="C113" s="64"/>
+      <c r="A113" s="47"/>
+      <c r="B113" s="47"/>
+      <c r="C113" s="65"/>
       <c r="D113" s="33" t="s">
         <v>237</v>
       </c>
@@ -4600,14 +4600,14 @@
       <c r="F113" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G113" s="62"/>
+      <c r="G113" s="47"/>
     </row>
     <row r="114" spans="1:7" ht="25.5">
-      <c r="A114" s="62"/>
-      <c r="B114" s="69" t="s">
+      <c r="A114" s="47"/>
+      <c r="B114" s="63" t="s">
         <v>238</v>
       </c>
-      <c r="C114" s="68" t="s">
+      <c r="C114" s="64" t="s">
         <v>54</v>
       </c>
       <c r="D114" s="33" t="s">
@@ -4619,12 +4619,12 @@
       <c r="F114" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G114" s="62"/>
+      <c r="G114" s="47"/>
     </row>
     <row r="115" spans="1:7" ht="15.4">
-      <c r="A115" s="72"/>
-      <c r="B115" s="72"/>
-      <c r="C115" s="74"/>
+      <c r="A115" s="62"/>
+      <c r="B115" s="62"/>
+      <c r="C115" s="67"/>
       <c r="D115" s="38" t="s">
         <v>240</v>
       </c>
@@ -4634,10 +4634,10 @@
       <c r="F115" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G115" s="72"/>
+      <c r="G115" s="62"/>
     </row>
     <row r="116" spans="1:7" ht="15.4">
-      <c r="A116" s="79" t="s">
+      <c r="A116" s="51" t="s">
         <v>242</v>
       </c>
       <c r="B116" s="39" t="s">
@@ -4655,12 +4655,12 @@
       <c r="F116" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G116" s="78" t="s">
+      <c r="G116" s="50" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.4">
-      <c r="A117" s="80"/>
+      <c r="A117" s="52"/>
       <c r="B117" s="41" t="s">
         <v>247</v>
       </c>
@@ -4676,10 +4676,10 @@
       <c r="F117" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G117" s="80"/>
+      <c r="G117" s="52"/>
     </row>
     <row r="118" spans="1:7" ht="15.4">
-      <c r="A118" s="80"/>
+      <c r="A118" s="52"/>
       <c r="B118" s="41" t="s">
         <v>250</v>
       </c>
@@ -4695,7 +4695,7 @@
       <c r="F118" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G118" s="80"/>
+      <c r="G118" s="52"/>
     </row>
     <row r="119" spans="1:7" ht="15.4">
       <c r="A119" s="42"/>
@@ -5005,6 +5005,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="O19:O24"/>
+    <mergeCell ref="I25:I30"/>
+    <mergeCell ref="J25:J30"/>
+    <mergeCell ref="O25:O30"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="J31:J35"/>
+    <mergeCell ref="O31:O35"/>
+    <mergeCell ref="I19:I24"/>
+    <mergeCell ref="J19:J24"/>
+    <mergeCell ref="H19:H24"/>
+    <mergeCell ref="A19:A35"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="G19:G24"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="B36:B44"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="A49:A80"/>
+    <mergeCell ref="B50:B59"/>
+    <mergeCell ref="C50:C59"/>
+    <mergeCell ref="G50:G59"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="G61:G66"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="B71:B75"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="G76:G80"/>
+    <mergeCell ref="A81:A97"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="G86:G88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="C91:C95"/>
+    <mergeCell ref="G91:G95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="A98:A107"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="G98:G107"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B102:B107"/>
+    <mergeCell ref="C102:C107"/>
     <mergeCell ref="C14:C18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="A116:A118"/>
@@ -5021,74 +5089,6 @@
     <mergeCell ref="B112:B113"/>
     <mergeCell ref="C112:C113"/>
     <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="A98:A107"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="G98:G107"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B102:B107"/>
-    <mergeCell ref="C102:C107"/>
-    <mergeCell ref="A81:A97"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="G82:G85"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="G86:G88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="C91:C95"/>
-    <mergeCell ref="G91:G95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="A49:A80"/>
-    <mergeCell ref="B50:B59"/>
-    <mergeCell ref="C50:C59"/>
-    <mergeCell ref="G50:G59"/>
-    <mergeCell ref="B61:B66"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="G61:G66"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="G76:G80"/>
-    <mergeCell ref="A36:A48"/>
-    <mergeCell ref="B36:B44"/>
-    <mergeCell ref="C36:C44"/>
-    <mergeCell ref="G36:G44"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="G45:G48"/>
-    <mergeCell ref="H19:H24"/>
-    <mergeCell ref="A19:A35"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="G19:G24"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="G25:G30"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="O19:O24"/>
-    <mergeCell ref="I25:I30"/>
-    <mergeCell ref="J25:J30"/>
-    <mergeCell ref="O25:O30"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="J31:J35"/>
-    <mergeCell ref="O31:O35"/>
-    <mergeCell ref="I19:I24"/>
-    <mergeCell ref="J19:J24"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <dataValidations count="2">

--- a/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
+++ b/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Develop\others\MyPGEE\main\408\ds\【数据结构应用题】打卡表及参考文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0469145-9C58-441D-895E-A2F98496F418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7953ED74-A2D6-4B84-B8DB-D69D4C40E1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="290">
   <si>
     <t>强化阶段（二轮复习）“应用题”备考打卡表</t>
   </si>
@@ -327,9 +327,6 @@
     <t>3.1.1</t>
   </si>
   <si>
-    <t>总结二叉树的度、树高、结点数等属性之间的关系（通过王道书 5.2.3 课后小题来复习“二叉树的性质”）</t>
-  </si>
-  <si>
     <t>通过王道书 5.2.3 课后小题来复习“二叉树的性质”</t>
   </si>
   <si>
@@ -393,9 +390,6 @@
     <t>通过王道书 5.1.4、5.4.4 课后小题来复习“树和森林的性质”</t>
   </si>
   <si>
-    <t>树（森林）的定义和画图</t>
-  </si>
-  <si>
     <t>3.3.1</t>
   </si>
   <si>
@@ -412,9 +406,6 @@
   </si>
   <si>
     <t>3.3.3</t>
-  </si>
-  <si>
-    <t>对比：树的孩子表示法存储 v.s. 图的邻接表存储 v.s. 散列表的拉链法 v.s. 基数排序。你发现了什么？</t>
   </si>
   <si>
     <t>3.3.4</t>
@@ -1649,6 +1640,22 @@
   </si>
   <si>
     <t>画出每一轮快速排序的状态</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>总结二叉树的度、树高、结点数等属性之间的关系（通过王道书 5.2.3 课后小题来复习“二叉树的性质”）</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>可扩展</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>对比：树的孩子表示法存储 v.s. 图的邻接表存储 v.s. 散列表的拉链法 v.s. 基数排序。你发现了什么？</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>树（森林）的定义和画图</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
@@ -1659,7 +1666,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1912,6 +1919,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2027,7 +2041,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2162,6 +2176,12 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2232,11 +2252,11 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -2634,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>2</v>
@@ -2653,14 +2673,14 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="53" t="s">
-        <v>254</v>
+      <c r="C3" s="55" t="s">
+        <v>251</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>9</v>
@@ -2669,16 +2689,16 @@
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.4">
-      <c r="A4" s="59"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="47"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="14" t="s">
         <v>12</v>
       </c>
@@ -2686,14 +2706,14 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
-      <c r="A5" s="59"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="47"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="14" t="s">
         <v>14</v>
       </c>
@@ -2701,14 +2721,14 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" ht="15.4">
-      <c r="A6" s="59"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="47"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
@@ -2716,14 +2736,14 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" ht="15.4">
-      <c r="A7" s="59"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="47"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="14" t="s">
         <v>18</v>
       </c>
@@ -2731,14 +2751,14 @@
         <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" ht="15.4">
-      <c r="A8" s="60"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="54"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="14" t="s">
         <v>20</v>
       </c>
@@ -2746,14 +2766,14 @@
         <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="47"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="14" t="s">
         <v>22</v>
       </c>
@@ -2761,14 +2781,14 @@
         <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" ht="15.4">
-      <c r="A10" s="59"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="47"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="14" t="s">
         <v>24</v>
       </c>
@@ -2776,14 +2796,14 @@
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" ht="15.4">
-      <c r="A11" s="59"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="47"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="14" t="s">
         <v>26</v>
       </c>
@@ -2791,14 +2811,14 @@
         <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" ht="15.4">
-      <c r="A12" s="59"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="47"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="14" t="s">
         <v>28</v>
       </c>
@@ -2806,14 +2826,14 @@
         <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" ht="15.4">
-      <c r="A13" s="59"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="47"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="14" t="s">
         <v>30</v>
       </c>
@@ -2821,14 +2841,14 @@
         <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7" ht="15.4">
-      <c r="A14" s="59"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="46" t="s">
+      <c r="A14" s="61"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="48" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -2838,16 +2858,16 @@
         <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G14" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="G14" s="51" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.4">
-      <c r="A15" s="59"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="47"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13" t="s">
         <v>36</v>
       </c>
@@ -2855,14 +2875,14 @@
         <v>37</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G15" s="47"/>
+        <v>279</v>
+      </c>
+      <c r="G15" s="49"/>
     </row>
     <row r="16" spans="1:7" ht="15.4">
-      <c r="A16" s="60"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="48"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="13" t="s">
         <v>38</v>
       </c>
@@ -2870,14 +2890,14 @@
         <v>39</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G16" s="50"/>
+        <v>279</v>
+      </c>
+      <c r="G16" s="52"/>
     </row>
     <row r="17" spans="1:15" ht="15.4">
-      <c r="A17" s="60"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="48"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
@@ -2885,14 +2905,14 @@
         <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G17" s="50"/>
+        <v>279</v>
+      </c>
+      <c r="G17" s="52"/>
     </row>
     <row r="18" spans="1:15" ht="15.4">
-      <c r="A18" s="59"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="47"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="49"/>
       <c r="D18" s="13" t="s">
         <v>42</v>
       </c>
@@ -2900,45 +2920,45 @@
         <v>43</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G18" s="49"/>
+    </row>
+    <row r="19" spans="1:15" ht="16.149999999999999">
+      <c r="A19" s="76" t="s">
         <v>282</v>
       </c>
-      <c r="G18" s="47"/>
-    </row>
-    <row r="19" spans="1:15" ht="16.149999999999999">
-      <c r="A19" s="74" t="s">
-        <v>285</v>
-      </c>
-      <c r="B19" s="76" t="s">
-        <v>284</v>
-      </c>
-      <c r="C19" s="77" t="s">
+      <c r="B19" s="78" t="s">
+        <v>281</v>
+      </c>
+      <c r="C19" s="79" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G19" s="79" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="72"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="85"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="87"/>
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
       <c r="M19" s="22"/>
       <c r="N19" s="23"/>
-      <c r="O19" s="82"/>
+      <c r="O19" s="84"/>
     </row>
     <row r="20" spans="1:15" ht="15.4">
-      <c r="A20" s="75"/>
-      <c r="B20" s="75"/>
-      <c r="C20" s="78"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="24" t="s">
         <v>46</v>
       </c>
@@ -2946,22 +2966,22 @@
         <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G20" s="75"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G20" s="77"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="22"/>
       <c r="N20" s="23"/>
-      <c r="O20" s="83"/>
+      <c r="O20" s="85"/>
     </row>
     <row r="21" spans="1:15" ht="15.4">
-      <c r="A21" s="75"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="78"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="24" t="s">
         <v>48</v>
       </c>
@@ -2969,22 +2989,22 @@
         <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G21" s="75"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G21" s="77"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
       <c r="M21" s="22"/>
       <c r="N21" s="23"/>
-      <c r="O21" s="83"/>
+      <c r="O21" s="85"/>
     </row>
     <row r="22" spans="1:15" ht="15.4">
-      <c r="A22" s="75"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="78"/>
+      <c r="A22" s="77"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="24" t="s">
         <v>50</v>
       </c>
@@ -2992,22 +3012,22 @@
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G22" s="75"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G22" s="77"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="22"/>
       <c r="N22" s="23"/>
-      <c r="O22" s="83"/>
+      <c r="O22" s="85"/>
     </row>
     <row r="23" spans="1:15" ht="15.4">
-      <c r="A23" s="75"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="78"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="24" t="s">
         <v>52</v>
       </c>
@@ -3015,73 +3035,73 @@
         <v>49</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G23" s="75"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G23" s="77"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="M23" s="27"/>
       <c r="N23" s="23"/>
-      <c r="O23" s="83"/>
+      <c r="O23" s="85"/>
     </row>
     <row r="24" spans="1:15" ht="15.4">
-      <c r="A24" s="75"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="78"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="24" t="s">
         <v>53</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G24" s="75"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G24" s="77"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
       <c r="M24" s="22"/>
       <c r="N24" s="23"/>
-      <c r="O24" s="83"/>
+      <c r="O24" s="85"/>
     </row>
     <row r="25" spans="1:15" ht="15.4">
-      <c r="A25" s="75"/>
-      <c r="B25" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C25" s="81" t="s">
+      <c r="A25" s="77"/>
+      <c r="B25" s="82" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="83" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>55</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G25" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="G25" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="84"/>
-      <c r="J25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="87"/>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="22"/>
       <c r="N25" s="23"/>
-      <c r="O25" s="82"/>
+      <c r="O25" s="84"/>
     </row>
     <row r="26" spans="1:15" ht="15.4">
-      <c r="A26" s="75"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="65"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="67"/>
       <c r="D26" s="24" t="s">
         <v>57</v>
       </c>
@@ -3089,21 +3109,21 @@
         <v>47</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G26" s="47"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="86"/>
+        <v>284</v>
+      </c>
+      <c r="G26" s="49"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="88"/>
       <c r="K26" s="26"/>
       <c r="L26" s="26"/>
       <c r="M26" s="22"/>
       <c r="N26" s="23"/>
-      <c r="O26" s="83"/>
+      <c r="O26" s="85"/>
     </row>
     <row r="27" spans="1:15" ht="15.4">
-      <c r="A27" s="75"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="65"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="67"/>
       <c r="D27" s="24" t="s">
         <v>58</v>
       </c>
@@ -3111,21 +3131,21 @@
         <v>49</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G27" s="47"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="86"/>
+        <v>284</v>
+      </c>
+      <c r="G27" s="49"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="88"/>
       <c r="K27" s="26"/>
       <c r="L27" s="26"/>
       <c r="M27" s="22"/>
       <c r="N27" s="23"/>
-      <c r="O27" s="83"/>
+      <c r="O27" s="85"/>
     </row>
     <row r="28" spans="1:15" ht="15.4">
-      <c r="A28" s="75"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="65"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="67"/>
       <c r="D28" s="24" t="s">
         <v>59</v>
       </c>
@@ -3133,21 +3153,21 @@
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G28" s="47"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="86"/>
+        <v>284</v>
+      </c>
+      <c r="G28" s="49"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="88"/>
       <c r="K28" s="26"/>
       <c r="L28" s="26"/>
       <c r="M28" s="22"/>
       <c r="N28" s="23"/>
-      <c r="O28" s="83"/>
+      <c r="O28" s="85"/>
     </row>
     <row r="29" spans="1:15" ht="15.4">
-      <c r="A29" s="75"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="65"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="67"/>
       <c r="D29" s="24" t="s">
         <v>60</v>
       </c>
@@ -3155,71 +3175,71 @@
         <v>49</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G29" s="47"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="86"/>
+        <v>284</v>
+      </c>
+      <c r="G29" s="49"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="88"/>
       <c r="K29" s="26"/>
       <c r="L29" s="26"/>
       <c r="M29" s="27"/>
       <c r="N29" s="23"/>
-      <c r="O29" s="83"/>
+      <c r="O29" s="85"/>
     </row>
     <row r="30" spans="1:15" ht="15.4">
-      <c r="A30" s="75"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="65"/>
+      <c r="A30" s="77"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="67"/>
       <c r="D30" s="24" t="s">
         <v>61</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G30" s="47"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="86"/>
+        <v>284</v>
+      </c>
+      <c r="G30" s="49"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="88"/>
       <c r="K30" s="26"/>
       <c r="L30" s="26"/>
       <c r="M30" s="27"/>
       <c r="N30" s="23"/>
-      <c r="O30" s="83"/>
+      <c r="O30" s="85"/>
     </row>
     <row r="31" spans="1:15" ht="15.4">
-      <c r="A31" s="75"/>
-      <c r="B31" s="47" t="s">
-        <v>259</v>
-      </c>
-      <c r="C31" s="81" t="s">
+      <c r="A31" s="77"/>
+      <c r="B31" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="C31" s="83" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>63</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G31" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="G31" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="87"/>
-      <c r="J31" s="85"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="87"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="27"/>
       <c r="N31" s="31"/>
-      <c r="O31" s="88"/>
+      <c r="O31" s="90"/>
     </row>
     <row r="32" spans="1:15" ht="15.4">
-      <c r="A32" s="75"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="65"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="67"/>
       <c r="D32" s="24" t="s">
         <v>65</v>
       </c>
@@ -3227,21 +3247,21 @@
         <v>47</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G32" s="47"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G32" s="49"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
       <c r="K32" s="26"/>
       <c r="L32" s="26"/>
       <c r="M32" s="27"/>
       <c r="N32" s="31"/>
-      <c r="O32" s="83"/>
+      <c r="O32" s="85"/>
     </row>
     <row r="33" spans="1:15" ht="15.4">
-      <c r="A33" s="75"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="65"/>
+      <c r="A33" s="77"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="67"/>
       <c r="D33" s="24" t="s">
         <v>66</v>
       </c>
@@ -3249,21 +3269,21 @@
         <v>49</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G33" s="47"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G33" s="49"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="27"/>
       <c r="N33" s="31"/>
-      <c r="O33" s="83"/>
+      <c r="O33" s="85"/>
     </row>
     <row r="34" spans="1:15" ht="15.4">
-      <c r="A34" s="75"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="65"/>
+      <c r="A34" s="77"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="67"/>
       <c r="D34" s="24" t="s">
         <v>67</v>
       </c>
@@ -3271,21 +3291,21 @@
         <v>51</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G34" s="47"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G34" s="49"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
       <c r="M34" s="27"/>
       <c r="N34" s="31"/>
-      <c r="O34" s="83"/>
+      <c r="O34" s="85"/>
     </row>
     <row r="35" spans="1:15" ht="15.4">
-      <c r="A35" s="75"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="65"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="67"/>
       <c r="D35" s="24" t="s">
         <v>68</v>
       </c>
@@ -3293,25 +3313,25 @@
         <v>49</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G35" s="47"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
+        <v>284</v>
+      </c>
+      <c r="G35" s="49"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
       <c r="K35" s="26"/>
       <c r="L35" s="26"/>
       <c r="M35" s="27"/>
       <c r="N35" s="31"/>
-      <c r="O35" s="83"/>
+      <c r="O35" s="85"/>
     </row>
     <row r="36" spans="1:15" ht="15.4">
-      <c r="A36" s="61" t="s">
+      <c r="A36" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="71" t="s">
+      <c r="B36" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="66" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="33" t="s">
@@ -3321,16 +3341,16 @@
         <v>72</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G36" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="G36" s="68" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15.4">
-      <c r="A37" s="47"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="65"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="67"/>
       <c r="D37" s="33" t="s">
         <v>74</v>
       </c>
@@ -3338,14 +3358,14 @@
         <v>75</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G37" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" spans="1:15" ht="15.4">
-      <c r="A38" s="47"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="65"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="67"/>
       <c r="D38" s="33" t="s">
         <v>76</v>
       </c>
@@ -3353,29 +3373,29 @@
         <v>77</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G38" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G38" s="49"/>
     </row>
     <row r="39" spans="1:15" ht="15.4">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="65"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="67"/>
       <c r="D39" s="33" t="s">
         <v>78</v>
       </c>
       <c r="E39" s="34" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G39" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G39" s="49"/>
     </row>
     <row r="40" spans="1:15" ht="15.4">
-      <c r="A40" s="47"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="65"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="67"/>
       <c r="D40" s="33" t="s">
         <v>79</v>
       </c>
@@ -3383,29 +3403,29 @@
         <v>80</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G40" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="1:15" ht="15.4">
-      <c r="A41" s="47"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="65"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="67"/>
       <c r="D41" s="33" t="s">
         <v>81</v>
       </c>
       <c r="E41" s="34" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G41" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G41" s="49"/>
     </row>
     <row r="42" spans="1:15" ht="15.4">
-      <c r="A42" s="47"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="65"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="67"/>
       <c r="D42" s="33" t="s">
         <v>82</v>
       </c>
@@ -3413,14 +3433,14 @@
         <v>83</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G42" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="1:15" ht="15.4">
-      <c r="A43" s="47"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="65"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="67"/>
       <c r="D43" s="33" t="s">
         <v>84</v>
       </c>
@@ -3428,14 +3448,14 @@
         <v>85</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G43" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G43" s="49"/>
     </row>
     <row r="44" spans="1:15" ht="15.4">
-      <c r="A44" s="47"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="65"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="67"/>
       <c r="D44" s="33" t="s">
         <v>86</v>
       </c>
@@ -3443,16 +3463,16 @@
         <v>87</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G44" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G44" s="49"/>
     </row>
     <row r="45" spans="1:15" ht="15.4">
-      <c r="A45" s="47"/>
-      <c r="B45" s="63" t="s">
+      <c r="A45" s="49"/>
+      <c r="B45" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -3462,16 +3482,16 @@
         <v>91</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G45" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="G45" s="68" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.4">
-      <c r="A46" s="47"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="65"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="67"/>
       <c r="D46" s="33" t="s">
         <v>93</v>
       </c>
@@ -3479,14 +3499,14 @@
         <v>94</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G46" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G46" s="49"/>
     </row>
     <row r="47" spans="1:15" ht="15.4">
-      <c r="A47" s="47"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="65"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="67"/>
       <c r="D47" s="33" t="s">
         <v>95</v>
       </c>
@@ -3494,14 +3514,14 @@
         <v>96</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G47" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G47" s="49"/>
     </row>
     <row r="48" spans="1:15" ht="15.4">
-      <c r="A48" s="47"/>
-      <c r="B48" s="47"/>
-      <c r="C48" s="65"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="67"/>
       <c r="D48" s="33" t="s">
         <v>97</v>
       </c>
@@ -3509,12 +3529,12 @@
         <v>94</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G48" s="47"/>
+        <v>284</v>
+      </c>
+      <c r="G48" s="49"/>
     </row>
     <row r="49" spans="1:7" ht="25.5">
-      <c r="A49" s="61" t="s">
+      <c r="A49" s="63" t="s">
         <v>98</v>
       </c>
       <c r="B49" s="33" t="s">
@@ -3526,1183 +3546,1183 @@
       <c r="D49" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="E49" s="35" t="s">
+      <c r="E49" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="F49" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="G49" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G49" s="30" t="s">
+    </row>
+    <row r="50" spans="1:7" ht="15.4">
+      <c r="A50" s="49"/>
+      <c r="B50" s="65" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.4">
-      <c r="A50" s="47"/>
-      <c r="B50" s="63" t="s">
+      <c r="C50" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" s="33" t="s">
+      <c r="E50" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G50" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G50" s="66" t="s">
+    </row>
+    <row r="51" spans="1:7" ht="15.4">
+      <c r="A51" s="49"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="67"/>
+      <c r="D51" s="33" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="15.4">
-      <c r="A51" s="47"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="65"/>
-      <c r="D51" s="33" t="s">
+      <c r="E51" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="E51" s="30" t="s">
+      <c r="F51" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G51" s="49"/>
+    </row>
+    <row r="52" spans="1:7" ht="15.4">
+      <c r="A52" s="49"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="67"/>
+      <c r="D52" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G51" s="47"/>
-    </row>
-    <row r="52" spans="1:7" ht="15.4">
-      <c r="A52" s="47"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="65"/>
-      <c r="D52" s="33" t="s">
+      <c r="E52" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="F52" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G52" s="49"/>
+    </row>
+    <row r="53" spans="1:7" ht="15.4">
+      <c r="A53" s="49"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="67"/>
+      <c r="D53" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G52" s="47"/>
-    </row>
-    <row r="53" spans="1:7" ht="15.4">
-      <c r="A53" s="47"/>
-      <c r="B53" s="47"/>
-      <c r="C53" s="65"/>
-      <c r="D53" s="33" t="s">
+      <c r="E53" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="E53" s="30" t="s">
+      <c r="F53" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G53" s="49"/>
+    </row>
+    <row r="54" spans="1:7" ht="15.4">
+      <c r="A54" s="49"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="67"/>
+      <c r="D54" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G53" s="47"/>
-    </row>
-    <row r="54" spans="1:7" ht="15.4">
-      <c r="A54" s="47"/>
-      <c r="B54" s="47"/>
-      <c r="C54" s="65"/>
-      <c r="D54" s="33" t="s">
+      <c r="E54" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="E54" s="30" t="s">
+      <c r="F54" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G54" s="49"/>
+    </row>
+    <row r="55" spans="1:7" ht="15.4">
+      <c r="A55" s="49"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G54" s="47"/>
-    </row>
-    <row r="55" spans="1:7" ht="15.4">
-      <c r="A55" s="47"/>
-      <c r="B55" s="47"/>
-      <c r="C55" s="65"/>
-      <c r="D55" s="33" t="s">
+      <c r="E55" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G55" s="49"/>
+    </row>
+    <row r="56" spans="1:7" ht="15.4">
+      <c r="A56" s="49"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G55" s="47"/>
-    </row>
-    <row r="56" spans="1:7" ht="15.4">
-      <c r="A56" s="47"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="33" t="s">
+      <c r="E56" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G56" s="49"/>
+    </row>
+    <row r="57" spans="1:7" ht="15.4">
+      <c r="A57" s="49"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E56" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G56" s="47"/>
-    </row>
-    <row r="57" spans="1:7" ht="15.4">
-      <c r="A57" s="47"/>
-      <c r="B57" s="47"/>
-      <c r="C57" s="65"/>
-      <c r="D57" s="33" t="s">
+      <c r="E57" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G57" s="49"/>
+    </row>
+    <row r="58" spans="1:7" ht="15.4">
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="67"/>
+      <c r="D58" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="E57" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G57" s="47"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.4">
-      <c r="A58" s="47"/>
-      <c r="B58" s="47"/>
-      <c r="C58" s="65"/>
-      <c r="D58" s="33" t="s">
+      <c r="E58" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G58" s="49"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.4">
+      <c r="A59" s="49"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="67"/>
+      <c r="D59" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E58" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G58" s="47"/>
-    </row>
-    <row r="59" spans="1:7" ht="15.4">
-      <c r="A59" s="47"/>
-      <c r="B59" s="47"/>
-      <c r="C59" s="65"/>
-      <c r="D59" s="33" t="s">
+      <c r="E59" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G59" s="49"/>
+    </row>
+    <row r="60" spans="1:7" ht="25.5">
+      <c r="A60" s="49"/>
+      <c r="B60" s="33" t="s">
         <v>118</v>
-      </c>
-      <c r="E59" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G59" s="47"/>
-    </row>
-    <row r="60" spans="1:7" ht="25.5">
-      <c r="A60" s="47"/>
-      <c r="B60" s="33" t="s">
-        <v>119</v>
       </c>
       <c r="C60" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D60" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="E60" s="35" t="s">
+      <c r="F60" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G60" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G60" s="30" t="s">
+    </row>
+    <row r="61" spans="1:7" ht="15.4">
+      <c r="A61" s="49"/>
+      <c r="B61" s="72" t="s">
+        <v>289</v>
+      </c>
+      <c r="C61" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="33" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.4">
-      <c r="A61" s="47"/>
-      <c r="B61" s="63" t="s">
+      <c r="E61" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="64" t="s">
+      <c r="F61" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G61" s="68" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.4">
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="67"/>
+      <c r="D62" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G62" s="49"/>
+    </row>
+    <row r="63" spans="1:7" ht="25.5">
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="67"/>
+      <c r="D63" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G63" s="49"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.4">
+      <c r="A64" s="49"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="67"/>
+      <c r="D64" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G64" s="49"/>
+    </row>
+    <row r="65" spans="1:7" ht="25.5">
+      <c r="A65" s="49"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="67"/>
+      <c r="D65" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G65" s="49"/>
+    </row>
+    <row r="66" spans="1:7" ht="25.5">
+      <c r="A66" s="49"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="67"/>
+      <c r="D66" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G66" s="49"/>
+    </row>
+    <row r="67" spans="1:7" ht="15.4">
+      <c r="A67" s="49"/>
+      <c r="B67" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G67" s="68" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.4">
+      <c r="A68" s="49"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="67"/>
+      <c r="D68" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G68" s="49"/>
+    </row>
+    <row r="69" spans="1:7" ht="15.4">
+      <c r="A69" s="49"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G69" s="49"/>
+    </row>
+    <row r="70" spans="1:7" ht="25.5">
+      <c r="A70" s="49"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G70" s="49"/>
+    </row>
+    <row r="71" spans="1:7" ht="15.4">
+      <c r="A71" s="49"/>
+      <c r="B71" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="C71" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="E71" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G71" s="68" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.4">
+      <c r="A72" s="49"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="67"/>
+      <c r="D72" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G72" s="49"/>
+    </row>
+    <row r="73" spans="1:7" ht="15.4">
+      <c r="A73" s="49"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="67"/>
+      <c r="D73" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G73" s="49"/>
+    </row>
+    <row r="74" spans="1:7" ht="25.5">
+      <c r="A74" s="49"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="67"/>
+      <c r="D74" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G74" s="49"/>
+    </row>
+    <row r="75" spans="1:7" ht="25.5">
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="67"/>
+      <c r="D75" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G75" s="49"/>
+    </row>
+    <row r="76" spans="1:7" ht="25.5">
+      <c r="A76" s="49"/>
+      <c r="B76" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="D61" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E61" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G61" s="66" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.4">
-      <c r="A62" s="47"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="65"/>
-      <c r="D62" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G62" s="47"/>
-    </row>
-    <row r="63" spans="1:7" ht="25.5">
-      <c r="A63" s="47"/>
-      <c r="B63" s="47"/>
-      <c r="C63" s="65"/>
-      <c r="D63" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G63" s="47"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.4">
-      <c r="A64" s="47"/>
-      <c r="B64" s="47"/>
-      <c r="C64" s="65"/>
-      <c r="D64" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G64" s="47"/>
-    </row>
-    <row r="65" spans="1:7" ht="25.5">
-      <c r="A65" s="47"/>
-      <c r="B65" s="47"/>
-      <c r="C65" s="65"/>
-      <c r="D65" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="E65" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G65" s="47"/>
-    </row>
-    <row r="66" spans="1:7" ht="25.5">
-      <c r="A66" s="47"/>
-      <c r="B66" s="47"/>
-      <c r="C66" s="65"/>
-      <c r="D66" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G66" s="47"/>
-    </row>
-    <row r="67" spans="1:7" ht="15.4">
-      <c r="A67" s="47"/>
-      <c r="B67" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="D67" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="E67" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G67" s="66" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15.4">
-      <c r="A68" s="47"/>
-      <c r="B68" s="47"/>
-      <c r="C68" s="65"/>
-      <c r="D68" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E68" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G68" s="47"/>
-    </row>
-    <row r="69" spans="1:7" ht="15.4">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="65"/>
-      <c r="D69" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E69" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G69" s="47"/>
-    </row>
-    <row r="70" spans="1:7" ht="25.5">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="E70" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G70" s="47"/>
-    </row>
-    <row r="71" spans="1:7" ht="15.4">
-      <c r="A71" s="47"/>
-      <c r="B71" s="63" t="s">
-        <v>147</v>
-      </c>
-      <c r="C71" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="D71" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="E71" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G71" s="66" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15.4">
-      <c r="A72" s="47"/>
-      <c r="B72" s="47"/>
-      <c r="C72" s="65"/>
-      <c r="D72" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="E72" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G72" s="47"/>
-    </row>
-    <row r="73" spans="1:7" ht="15.4">
-      <c r="A73" s="47"/>
-      <c r="B73" s="47"/>
-      <c r="C73" s="65"/>
-      <c r="D73" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="E73" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G73" s="47"/>
-    </row>
-    <row r="74" spans="1:7" ht="25.5">
-      <c r="A74" s="47"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="65"/>
-      <c r="D74" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="E74" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G74" s="47"/>
-    </row>
-    <row r="75" spans="1:7" ht="25.5">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="65"/>
-      <c r="D75" s="33" t="s">
+      <c r="D76" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="E75" s="30" t="s">
+      <c r="E76" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G76" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G75" s="47"/>
-    </row>
-    <row r="76" spans="1:7" ht="25.5">
-      <c r="A76" s="47"/>
-      <c r="B76" s="70" t="s">
+    </row>
+    <row r="77" spans="1:7" ht="15.4">
+      <c r="A77" s="49"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="67"/>
+      <c r="D77" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="33" t="s">
+      <c r="E77" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="E76" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G76" s="66" t="s">
+      <c r="F77" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G77" s="49"/>
+    </row>
+    <row r="78" spans="1:7" ht="38.25">
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="67"/>
+      <c r="D78" s="33" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="15.4">
-      <c r="A77" s="47"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="65"/>
-      <c r="D77" s="33" t="s">
+      <c r="E78" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="E77" s="30" t="s">
+      <c r="F78" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G78" s="49"/>
+    </row>
+    <row r="79" spans="1:7" ht="38.25">
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="67"/>
+      <c r="D79" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G77" s="47"/>
-    </row>
-    <row r="78" spans="1:7" ht="38.25">
-      <c r="A78" s="47"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="65"/>
-      <c r="D78" s="33" t="s">
+      <c r="E79" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G79" s="49"/>
+    </row>
+    <row r="80" spans="1:7" ht="15.4">
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="E78" s="30" t="s">
+      <c r="E80" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G78" s="47"/>
-    </row>
-    <row r="79" spans="1:7" ht="38.25">
-      <c r="A79" s="47"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="65"/>
-      <c r="D79" s="33" t="s">
+      <c r="F80" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G80" s="49"/>
+    </row>
+    <row r="81" spans="1:7" ht="25.5">
+      <c r="A81" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" s="33" t="s">
         <v>166</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G79" s="47"/>
-    </row>
-    <row r="80" spans="1:7" ht="15.4">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="65"/>
-      <c r="D80" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E80" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G80" s="47"/>
-    </row>
-    <row r="81" spans="1:7" ht="25.5">
-      <c r="A81" s="61" t="s">
-        <v>283</v>
-      </c>
-      <c r="B81" s="33" t="s">
-        <v>169</v>
       </c>
       <c r="C81" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D81" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E81" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G81" s="30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.4">
+      <c r="A82" s="49"/>
+      <c r="B82" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="E81" s="35" t="s">
+      <c r="C82" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G81" s="30" t="s">
+      <c r="E82" s="30" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="15.4">
-      <c r="A82" s="47"/>
-      <c r="B82" s="63" t="s">
+      <c r="F82" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G82" s="68" t="s">
         <v>173</v>
       </c>
-      <c r="C82" s="64" t="s">
+    </row>
+    <row r="83" spans="1:7" ht="15.4">
+      <c r="A83" s="49"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G83" s="49"/>
+    </row>
+    <row r="84" spans="1:7" ht="15.4">
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="67"/>
+      <c r="D84" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G84" s="49"/>
+    </row>
+    <row r="85" spans="1:7" ht="15.4">
+      <c r="A85" s="49"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="67"/>
+      <c r="D85" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G85" s="49"/>
+    </row>
+    <row r="86" spans="1:7" ht="15.4">
+      <c r="A86" s="49"/>
+      <c r="B86" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G86" s="68" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="25.5">
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="67"/>
+      <c r="D87" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G87" s="49"/>
+    </row>
+    <row r="88" spans="1:7" ht="25.5">
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G88" s="49"/>
+    </row>
+    <row r="89" spans="1:7" ht="25.5">
+      <c r="A89" s="49"/>
+      <c r="B89" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G89" s="70" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15.4">
+      <c r="A90" s="49"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="67"/>
+      <c r="D90" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E90" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G90" s="64"/>
+    </row>
+    <row r="91" spans="1:7" ht="15.4">
+      <c r="A91" s="49"/>
+      <c r="B91" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="C91" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G91" s="68" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15.4">
+      <c r="A92" s="49"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="67"/>
+      <c r="D92" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E92" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G92" s="49"/>
+    </row>
+    <row r="93" spans="1:7" ht="15.4">
+      <c r="A93" s="49"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="E93" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G93" s="49"/>
+    </row>
+    <row r="94" spans="1:7" ht="15.4">
+      <c r="A94" s="49"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="67"/>
+      <c r="D94" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G94" s="49"/>
+    </row>
+    <row r="95" spans="1:7" ht="15.4">
+      <c r="A95" s="49"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G95" s="49"/>
+    </row>
+    <row r="96" spans="1:7" ht="15.4">
+      <c r="A96" s="49"/>
+      <c r="B96" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="C96" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E96" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G96" s="68" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15.4">
+      <c r="A97" s="49"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="67"/>
+      <c r="D97" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E97" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G97" s="49"/>
+    </row>
+    <row r="98" spans="1:7" ht="15.4">
+      <c r="A98" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="B98" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="C98" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D98" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G98" s="68" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15.4">
+      <c r="A99" s="49"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="67"/>
+      <c r="D99" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E99" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G99" s="49"/>
+    </row>
+    <row r="100" spans="1:7" ht="15.4">
+      <c r="A100" s="49"/>
+      <c r="B100" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G100" s="49"/>
+    </row>
+    <row r="101" spans="1:7" ht="15.4">
+      <c r="A101" s="49"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="67"/>
+      <c r="D101" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G101" s="49"/>
+    </row>
+    <row r="102" spans="1:7" ht="25.5">
+      <c r="A102" s="49"/>
+      <c r="B102" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="C102" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D102" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G102" s="49"/>
+    </row>
+    <row r="103" spans="1:7" ht="25.5">
+      <c r="A103" s="49"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="67"/>
+      <c r="D103" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G103" s="49"/>
+    </row>
+    <row r="104" spans="1:7" ht="15.4">
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="67"/>
+      <c r="D104" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E104" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G104" s="49"/>
+    </row>
+    <row r="105" spans="1:7" ht="25.5">
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="67"/>
+      <c r="D105" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G105" s="49"/>
+    </row>
+    <row r="106" spans="1:7" ht="25.5">
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="67"/>
+      <c r="D106" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G106" s="49"/>
+    </row>
+    <row r="107" spans="1:7" ht="15.4">
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="67"/>
+      <c r="D107" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E107" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G107" s="49"/>
+    </row>
+    <row r="108" spans="1:7" ht="15.4">
+      <c r="A108" s="63" t="s">
+        <v>222</v>
+      </c>
+      <c r="B108" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C108" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D108" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G108" s="68" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15.4">
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="67"/>
+      <c r="D109" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="E109" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G109" s="49"/>
+    </row>
+    <row r="110" spans="1:7" ht="25.5">
+      <c r="A110" s="49"/>
+      <c r="B110" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C110" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D82" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E82" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G82" s="66" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15.4">
-      <c r="A83" s="47"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E83" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G83" s="47"/>
-    </row>
-    <row r="84" spans="1:7" ht="15.4">
-      <c r="A84" s="47"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="65"/>
-      <c r="D84" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G84" s="47"/>
-    </row>
-    <row r="85" spans="1:7" ht="15.4">
-      <c r="A85" s="47"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="65"/>
-      <c r="D85" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G85" s="47"/>
-    </row>
-    <row r="86" spans="1:7" ht="15.4">
-      <c r="A86" s="47"/>
-      <c r="B86" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="C86" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="E86" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G86" s="66" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="25.5">
-      <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="65"/>
-      <c r="D87" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="E87" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G87" s="47"/>
-    </row>
-    <row r="88" spans="1:7" ht="25.5">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="E88" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G88" s="47"/>
-    </row>
-    <row r="89" spans="1:7" ht="25.5">
-      <c r="A89" s="47"/>
-      <c r="B89" s="63" t="s">
-        <v>188</v>
-      </c>
-      <c r="C89" s="64" t="s">
+      <c r="D110" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G110" s="49"/>
+    </row>
+    <row r="111" spans="1:7" ht="15.4">
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="67"/>
+      <c r="D111" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E111" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G111" s="49"/>
+    </row>
+    <row r="112" spans="1:7" ht="15.4">
+      <c r="A112" s="49"/>
+      <c r="B112" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="C112" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D89" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G89" s="68" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15.4">
-      <c r="A90" s="47"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="65"/>
-      <c r="D90" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="E90" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G90" s="62"/>
-    </row>
-    <row r="91" spans="1:7" ht="15.4">
-      <c r="A91" s="47"/>
-      <c r="B91" s="69" t="s">
-        <v>193</v>
-      </c>
-      <c r="C91" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="D91" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G91" s="66" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15.4">
-      <c r="A92" s="47"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="65"/>
-      <c r="D92" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="E92" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G92" s="47"/>
-    </row>
-    <row r="93" spans="1:7" ht="15.4">
-      <c r="A93" s="47"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="65"/>
-      <c r="D93" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="E93" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G93" s="47"/>
-    </row>
-    <row r="94" spans="1:7" ht="15.4">
-      <c r="A94" s="47"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="65"/>
-      <c r="D94" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="E94" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G94" s="47"/>
-    </row>
-    <row r="95" spans="1:7" ht="15.4">
-      <c r="A95" s="47"/>
-      <c r="B95" s="47"/>
-      <c r="C95" s="65"/>
-      <c r="D95" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E95" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G95" s="47"/>
-    </row>
-    <row r="96" spans="1:7" ht="15.4">
-      <c r="A96" s="47"/>
-      <c r="B96" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="C96" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="E96" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G96" s="66" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="15.4">
-      <c r="A97" s="47"/>
-      <c r="B97" s="47"/>
-      <c r="C97" s="65"/>
-      <c r="D97" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="E97" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G97" s="47"/>
-    </row>
-    <row r="98" spans="1:7" ht="15.4">
-      <c r="A98" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="B98" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="C98" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G98" s="66" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="15.4">
-      <c r="A99" s="47"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="E99" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G99" s="47"/>
-    </row>
-    <row r="100" spans="1:7" ht="15.4">
-      <c r="A100" s="47"/>
-      <c r="B100" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="C100" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D100" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G100" s="47"/>
-    </row>
-    <row r="101" spans="1:7" ht="15.4">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="65"/>
-      <c r="D101" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E101" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G101" s="47"/>
-    </row>
-    <row r="102" spans="1:7" ht="25.5">
-      <c r="A102" s="47"/>
-      <c r="B102" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="C102" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G102" s="47"/>
-    </row>
-    <row r="103" spans="1:7" ht="25.5">
-      <c r="A103" s="47"/>
-      <c r="B103" s="47"/>
-      <c r="C103" s="65"/>
-      <c r="D103" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G103" s="47"/>
-    </row>
-    <row r="104" spans="1:7" ht="15.4">
-      <c r="A104" s="47"/>
-      <c r="B104" s="47"/>
-      <c r="C104" s="65"/>
-      <c r="D104" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="E104" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G104" s="47"/>
-    </row>
-    <row r="105" spans="1:7" ht="25.5">
-      <c r="A105" s="47"/>
-      <c r="B105" s="47"/>
-      <c r="C105" s="65"/>
-      <c r="D105" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E105" s="7" t="s">
+      <c r="D112" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E112" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G105" s="47"/>
-    </row>
-    <row r="106" spans="1:7" ht="25.5">
-      <c r="A106" s="47"/>
-      <c r="B106" s="47"/>
-      <c r="C106" s="65"/>
-      <c r="D106" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E106" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G106" s="47"/>
-    </row>
-    <row r="107" spans="1:7" ht="15.4">
-      <c r="A107" s="47"/>
-      <c r="B107" s="47"/>
-      <c r="C107" s="65"/>
-      <c r="D107" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="E107" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G107" s="47"/>
-    </row>
-    <row r="108" spans="1:7" ht="15.4">
-      <c r="A108" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="B108" s="63" t="s">
-        <v>226</v>
-      </c>
-      <c r="C108" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D108" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="E108" s="7" t="s">
+      <c r="F112" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G112" s="49"/>
+    </row>
+    <row r="113" spans="1:7" ht="15.4">
+      <c r="A113" s="49"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="67"/>
+      <c r="D113" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E113" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G113" s="49"/>
+    </row>
+    <row r="114" spans="1:7" ht="25.5">
+      <c r="A114" s="49"/>
+      <c r="B114" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="C114" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="D114" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E114" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G108" s="66" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="15.4">
-      <c r="A109" s="47"/>
-      <c r="B109" s="47"/>
-      <c r="C109" s="65"/>
-      <c r="D109" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="E109" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G109" s="47"/>
-    </row>
-    <row r="110" spans="1:7" ht="25.5">
-      <c r="A110" s="47"/>
-      <c r="B110" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="C110" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="D110" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G110" s="47"/>
-    </row>
-    <row r="111" spans="1:7" ht="15.4">
-      <c r="A111" s="47"/>
-      <c r="B111" s="47"/>
-      <c r="C111" s="65"/>
-      <c r="D111" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="E111" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G111" s="47"/>
-    </row>
-    <row r="112" spans="1:7" ht="15.4">
-      <c r="A112" s="47"/>
-      <c r="B112" s="63" t="s">
-        <v>235</v>
-      </c>
-      <c r="C112" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D112" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G112" s="47"/>
-    </row>
-    <row r="113" spans="1:7" ht="15.4">
-      <c r="A113" s="47"/>
-      <c r="B113" s="47"/>
-      <c r="C113" s="65"/>
-      <c r="D113" s="33" t="s">
+      <c r="F114" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G114" s="49"/>
+    </row>
+    <row r="115" spans="1:7" ht="15.4">
+      <c r="A115" s="64"/>
+      <c r="B115" s="64"/>
+      <c r="C115" s="69"/>
+      <c r="D115" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="E113" s="44" t="s">
-        <v>288</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G113" s="47"/>
-    </row>
-    <row r="114" spans="1:7" ht="25.5">
-      <c r="A114" s="47"/>
-      <c r="B114" s="63" t="s">
+      <c r="E115" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="C114" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="D114" s="33" t="s">
+      <c r="F115" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G115" s="64"/>
+    </row>
+    <row r="116" spans="1:7" ht="15.4">
+      <c r="A116" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="E114" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G114" s="47"/>
-    </row>
-    <row r="115" spans="1:7" ht="15.4">
-      <c r="A115" s="62"/>
-      <c r="B115" s="62"/>
-      <c r="C115" s="67"/>
-      <c r="D115" s="38" t="s">
+      <c r="B116" s="39" t="s">
         <v>240</v>
-      </c>
-      <c r="E115" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G115" s="62"/>
-    </row>
-    <row r="116" spans="1:7" ht="15.4">
-      <c r="A116" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="B116" s="39" t="s">
-        <v>243</v>
       </c>
       <c r="C116" s="40" t="s">
         <v>89</v>
       </c>
       <c r="D116" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G116" s="52" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15.4">
+      <c r="A117" s="54"/>
+      <c r="B117" s="41" t="s">
         <v>244</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G116" s="50" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="15.4">
-      <c r="A117" s="52"/>
-      <c r="B117" s="41" t="s">
-        <v>247</v>
       </c>
       <c r="C117" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D117" s="33" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G117" s="52"/>
+        <v>279</v>
+      </c>
+      <c r="G117" s="54"/>
     </row>
     <row r="118" spans="1:7" ht="15.4">
-      <c r="A118" s="52"/>
+      <c r="A118" s="54"/>
       <c r="B118" s="41" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C118" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D118" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G118" s="52"/>
+        <v>279</v>
+      </c>
+      <c r="G118" s="54"/>
     </row>
     <row r="119" spans="1:7" ht="15.4">
       <c r="A119" s="42"/>
       <c r="C119" s="43"/>
       <c r="E119" s="42"/>
       <c r="F119" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G119" s="42"/>
     </row>
@@ -4711,7 +4731,7 @@
       <c r="C120" s="43"/>
       <c r="E120" s="42"/>
       <c r="F120" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G120" s="42"/>
     </row>
@@ -4720,7 +4740,7 @@
       <c r="C121" s="43"/>
       <c r="E121" s="42"/>
       <c r="F121" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G121" s="42"/>
     </row>
@@ -4729,7 +4749,7 @@
       <c r="C122" s="43"/>
       <c r="E122" s="42"/>
       <c r="F122" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G122" s="42"/>
     </row>
@@ -4738,7 +4758,7 @@
       <c r="C123" s="43"/>
       <c r="E123" s="42"/>
       <c r="F123" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G123" s="42"/>
     </row>
@@ -4747,7 +4767,7 @@
       <c r="C124" s="43"/>
       <c r="E124" s="42"/>
       <c r="F124" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G124" s="42"/>
     </row>
@@ -4756,7 +4776,7 @@
       <c r="C125" s="43"/>
       <c r="E125" s="42"/>
       <c r="F125" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G125" s="42"/>
     </row>
@@ -4765,7 +4785,7 @@
       <c r="C126" s="43"/>
       <c r="E126" s="42"/>
       <c r="F126" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G126" s="42"/>
     </row>
@@ -4774,7 +4794,7 @@
       <c r="C127" s="43"/>
       <c r="E127" s="42"/>
       <c r="F127" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G127" s="42"/>
     </row>
@@ -4783,7 +4803,7 @@
       <c r="C128" s="43"/>
       <c r="E128" s="42"/>
       <c r="F128" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G128" s="42"/>
     </row>
@@ -4792,7 +4812,7 @@
       <c r="C129" s="43"/>
       <c r="E129" s="42"/>
       <c r="F129" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G129" s="42"/>
     </row>
@@ -4801,7 +4821,7 @@
       <c r="C130" s="43"/>
       <c r="E130" s="42"/>
       <c r="F130" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G130" s="42"/>
     </row>
@@ -4810,7 +4830,7 @@
       <c r="C131" s="43"/>
       <c r="E131" s="42"/>
       <c r="F131" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G131" s="42"/>
     </row>
@@ -4819,7 +4839,7 @@
       <c r="C132" s="43"/>
       <c r="E132" s="42"/>
       <c r="F132" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G132" s="42"/>
     </row>
@@ -4828,7 +4848,7 @@
       <c r="C133" s="43"/>
       <c r="E133" s="42"/>
       <c r="F133" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G133" s="42"/>
     </row>
@@ -4837,7 +4857,7 @@
       <c r="C134" s="43"/>
       <c r="E134" s="42"/>
       <c r="F134" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G134" s="42"/>
     </row>
@@ -4846,7 +4866,7 @@
       <c r="C135" s="43"/>
       <c r="E135" s="42"/>
       <c r="F135" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G135" s="42"/>
     </row>
@@ -4855,7 +4875,7 @@
       <c r="C136" s="43"/>
       <c r="E136" s="42"/>
       <c r="F136" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G136" s="42"/>
     </row>
@@ -4864,7 +4884,7 @@
       <c r="C137" s="43"/>
       <c r="E137" s="42"/>
       <c r="F137" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G137" s="42"/>
     </row>
@@ -4873,7 +4893,7 @@
       <c r="C138" s="43"/>
       <c r="E138" s="42"/>
       <c r="F138" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G138" s="42"/>
     </row>
@@ -4882,7 +4902,7 @@
       <c r="C139" s="43"/>
       <c r="E139" s="42"/>
       <c r="F139" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G139" s="42"/>
     </row>
@@ -4891,7 +4911,7 @@
       <c r="C140" s="43"/>
       <c r="E140" s="42"/>
       <c r="F140" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G140" s="42"/>
     </row>
@@ -4900,7 +4920,7 @@
       <c r="C141" s="43"/>
       <c r="E141" s="42"/>
       <c r="F141" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G141" s="42"/>
     </row>
@@ -4909,7 +4929,7 @@
       <c r="C142" s="43"/>
       <c r="E142" s="42"/>
       <c r="F142" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G142" s="42"/>
     </row>
@@ -4918,7 +4938,7 @@
       <c r="C143" s="43"/>
       <c r="E143" s="42"/>
       <c r="F143" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G143" s="42"/>
     </row>
@@ -4927,7 +4947,7 @@
       <c r="C144" s="43"/>
       <c r="E144" s="42"/>
       <c r="F144" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G144" s="42"/>
     </row>
@@ -4936,7 +4956,7 @@
       <c r="C145" s="43"/>
       <c r="E145" s="42"/>
       <c r="F145" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G145" s="42"/>
     </row>
@@ -4945,7 +4965,7 @@
       <c r="C146" s="43"/>
       <c r="E146" s="42"/>
       <c r="F146" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G146" s="42"/>
     </row>
@@ -4954,7 +4974,7 @@
       <c r="C147" s="43"/>
       <c r="E147" s="42"/>
       <c r="F147" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G147" s="42"/>
     </row>
@@ -4963,7 +4983,7 @@
       <c r="C148" s="43"/>
       <c r="E148" s="42"/>
       <c r="F148" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G148" s="42"/>
     </row>
@@ -4972,7 +4992,7 @@
       <c r="C149" s="43"/>
       <c r="E149" s="42"/>
       <c r="F149" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G149" s="42"/>
     </row>
@@ -4981,7 +5001,7 @@
       <c r="C150" s="43"/>
       <c r="E150" s="42"/>
       <c r="F150" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G150" s="42"/>
     </row>
@@ -4990,7 +5010,7 @@
       <c r="C151" s="43"/>
       <c r="E151" s="42"/>
       <c r="F151" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G151" s="42"/>
     </row>
@@ -4999,7 +5019,7 @@
       <c r="C152" s="43"/>
       <c r="E152" s="42"/>
       <c r="F152" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G152" s="42"/>
     </row>

--- a/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
+++ b/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Develop\others\MyPGEE\main\408\ds\【数据结构应用题】打卡表及参考文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7953ED74-A2D6-4B84-B8DB-D69D4C40E1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFBB20B-E30E-474E-B3BA-585ACE3844BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2182,11 +2182,95 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2223,90 +2307,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2673,13 +2673,13 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="83" t="s">
         <v>251</v>
       </c>
       <c r="D3" s="14" t="s">
@@ -2696,9 +2696,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.4">
-      <c r="A4" s="61"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="49"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="64"/>
       <c r="D4" s="14" t="s">
         <v>12</v>
       </c>
@@ -2711,9 +2711,9 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
-      <c r="A5" s="61"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="49"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="64"/>
       <c r="D5" s="14" t="s">
         <v>14</v>
       </c>
@@ -2726,9 +2726,9 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" ht="15.4">
-      <c r="A6" s="61"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="49"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
@@ -2741,9 +2741,9 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" ht="15.4">
-      <c r="A7" s="61"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="49"/>
+      <c r="A7" s="89"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="14" t="s">
         <v>18</v>
       </c>
@@ -2756,9 +2756,9 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" ht="15.4">
-      <c r="A8" s="62"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="56"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="84"/>
       <c r="D8" s="14" t="s">
         <v>20</v>
       </c>
@@ -2771,9 +2771,9 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
-      <c r="A9" s="61"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="49"/>
+      <c r="A9" s="89"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="64"/>
       <c r="D9" s="14" t="s">
         <v>22</v>
       </c>
@@ -2786,9 +2786,9 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" ht="15.4">
-      <c r="A10" s="61"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="49"/>
+      <c r="A10" s="89"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="14" t="s">
         <v>24</v>
       </c>
@@ -2801,9 +2801,9 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" ht="15.4">
-      <c r="A11" s="61"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="89"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="14" t="s">
         <v>26</v>
       </c>
@@ -2816,9 +2816,9 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" ht="15.4">
-      <c r="A12" s="61"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="14" t="s">
         <v>28</v>
       </c>
@@ -2831,9 +2831,9 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" ht="15.4">
-      <c r="A13" s="61"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="89"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="14" t="s">
         <v>30</v>
       </c>
@@ -2846,9 +2846,9 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7" ht="15.4">
-      <c r="A14" s="61"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="48" t="s">
+      <c r="A14" s="89"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="77" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -2860,14 +2860,14 @@
       <c r="F14" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G14" s="51" t="s">
+      <c r="G14" s="79" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.4">
-      <c r="A15" s="61"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="49"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="13" t="s">
         <v>36</v>
       </c>
@@ -2877,12 +2877,12 @@
       <c r="F15" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G15" s="49"/>
+      <c r="G15" s="64"/>
     </row>
     <row r="16" spans="1:7" ht="15.4">
-      <c r="A16" s="62"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="50"/>
+      <c r="A16" s="90"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="78"/>
       <c r="D16" s="13" t="s">
         <v>38</v>
       </c>
@@ -2892,12 +2892,12 @@
       <c r="F16" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G16" s="52"/>
+      <c r="G16" s="80"/>
     </row>
     <row r="17" spans="1:15" ht="15.4">
-      <c r="A17" s="62"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="50"/>
+      <c r="A17" s="90"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="78"/>
       <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
@@ -2907,12 +2907,12 @@
       <c r="F17" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G17" s="52"/>
+      <c r="G17" s="80"/>
     </row>
     <row r="18" spans="1:15" ht="15.4">
-      <c r="A18" s="61"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="49"/>
+      <c r="A18" s="89"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="13" t="s">
         <v>42</v>
       </c>
@@ -2922,16 +2922,16 @@
       <c r="F18" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G18" s="49"/>
+      <c r="G18" s="64"/>
     </row>
     <row r="19" spans="1:15" ht="16.149999999999999">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="57" t="s">
         <v>282</v>
       </c>
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="59" t="s">
         <v>281</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="60" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="20" t="s">
@@ -2943,22 +2943,22 @@
       <c r="F19" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G19" s="81" t="s">
+      <c r="G19" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="74"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="87"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
       <c r="M19" s="22"/>
       <c r="N19" s="23"/>
-      <c r="O19" s="84"/>
+      <c r="O19" s="48"/>
     </row>
     <row r="20" spans="1:15" ht="15.4">
-      <c r="A20" s="77"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="24" t="s">
         <v>46</v>
       </c>
@@ -2968,20 +2968,20 @@
       <c r="F20" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G20" s="77"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="85"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="22"/>
       <c r="N20" s="23"/>
-      <c r="O20" s="85"/>
+      <c r="O20" s="49"/>
     </row>
     <row r="21" spans="1:15" ht="15.4">
-      <c r="A21" s="77"/>
-      <c r="B21" s="77"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="24" t="s">
         <v>48</v>
       </c>
@@ -2991,20 +2991,20 @@
       <c r="F21" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G21" s="77"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="85"/>
-      <c r="J21" s="85"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
       <c r="M21" s="22"/>
       <c r="N21" s="23"/>
-      <c r="O21" s="85"/>
+      <c r="O21" s="49"/>
     </row>
     <row r="22" spans="1:15" ht="15.4">
-      <c r="A22" s="77"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="24" t="s">
         <v>50</v>
       </c>
@@ -3014,20 +3014,20 @@
       <c r="F22" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="85"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="22"/>
       <c r="N22" s="23"/>
-      <c r="O22" s="85"/>
+      <c r="O22" s="49"/>
     </row>
     <row r="23" spans="1:15" ht="15.4">
-      <c r="A23" s="77"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="80"/>
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="61"/>
       <c r="D23" s="24" t="s">
         <v>52</v>
       </c>
@@ -3037,20 +3037,20 @@
       <c r="F23" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G23" s="77"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="85"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="M23" s="27"/>
       <c r="N23" s="23"/>
-      <c r="O23" s="85"/>
+      <c r="O23" s="49"/>
     </row>
     <row r="24" spans="1:15" ht="15.4">
-      <c r="A24" s="77"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="80"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="61"/>
       <c r="D24" s="24" t="s">
         <v>53</v>
       </c>
@@ -3060,22 +3060,22 @@
       <c r="F24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="85"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
       <c r="M24" s="22"/>
       <c r="N24" s="23"/>
-      <c r="O24" s="85"/>
+      <c r="O24" s="49"/>
     </row>
     <row r="25" spans="1:15" ht="15.4">
-      <c r="A25" s="77"/>
-      <c r="B25" s="82" t="s">
+      <c r="A25" s="58"/>
+      <c r="B25" s="63" t="s">
         <v>253</v>
       </c>
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="29" t="s">
@@ -3087,21 +3087,21 @@
       <c r="F25" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="G25" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="86"/>
-      <c r="J25" s="87"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="51"/>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="22"/>
       <c r="N25" s="23"/>
-      <c r="O25" s="84"/>
+      <c r="O25" s="48"/>
     </row>
     <row r="26" spans="1:15" ht="15.4">
-      <c r="A26" s="77"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="67"/>
+      <c r="A26" s="58"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="66"/>
       <c r="D26" s="24" t="s">
         <v>57</v>
       </c>
@@ -3111,19 +3111,19 @@
       <c r="F26" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G26" s="49"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="88"/>
+      <c r="G26" s="64"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="52"/>
       <c r="K26" s="26"/>
       <c r="L26" s="26"/>
       <c r="M26" s="22"/>
       <c r="N26" s="23"/>
-      <c r="O26" s="85"/>
+      <c r="O26" s="49"/>
     </row>
     <row r="27" spans="1:15" ht="15.4">
-      <c r="A27" s="77"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="67"/>
+      <c r="A27" s="58"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="24" t="s">
         <v>58</v>
       </c>
@@ -3133,19 +3133,19 @@
       <c r="F27" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G27" s="49"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="88"/>
+      <c r="G27" s="64"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="52"/>
       <c r="K27" s="26"/>
       <c r="L27" s="26"/>
       <c r="M27" s="22"/>
       <c r="N27" s="23"/>
-      <c r="O27" s="85"/>
+      <c r="O27" s="49"/>
     </row>
     <row r="28" spans="1:15" ht="15.4">
-      <c r="A28" s="77"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="67"/>
+      <c r="A28" s="58"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="66"/>
       <c r="D28" s="24" t="s">
         <v>59</v>
       </c>
@@ -3155,19 +3155,19 @@
       <c r="F28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G28" s="49"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="88"/>
+      <c r="G28" s="64"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="52"/>
       <c r="K28" s="26"/>
       <c r="L28" s="26"/>
       <c r="M28" s="22"/>
       <c r="N28" s="23"/>
-      <c r="O28" s="85"/>
+      <c r="O28" s="49"/>
     </row>
     <row r="29" spans="1:15" ht="15.4">
-      <c r="A29" s="77"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="67"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="66"/>
       <c r="D29" s="24" t="s">
         <v>60</v>
       </c>
@@ -3177,19 +3177,19 @@
       <c r="F29" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G29" s="49"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="88"/>
+      <c r="G29" s="64"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="52"/>
       <c r="K29" s="26"/>
       <c r="L29" s="26"/>
       <c r="M29" s="27"/>
       <c r="N29" s="23"/>
-      <c r="O29" s="85"/>
+      <c r="O29" s="49"/>
     </row>
     <row r="30" spans="1:15" ht="15.4">
-      <c r="A30" s="77"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="67"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="66"/>
       <c r="D30" s="24" t="s">
         <v>61</v>
       </c>
@@ -3199,21 +3199,21 @@
       <c r="F30" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G30" s="49"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="88"/>
+      <c r="G30" s="64"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="52"/>
       <c r="K30" s="26"/>
       <c r="L30" s="26"/>
       <c r="M30" s="27"/>
       <c r="N30" s="23"/>
-      <c r="O30" s="85"/>
+      <c r="O30" s="49"/>
     </row>
     <row r="31" spans="1:15" ht="15.4">
-      <c r="A31" s="77"/>
-      <c r="B31" s="49" t="s">
+      <c r="A31" s="58"/>
+      <c r="B31" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="65" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="29" t="s">
@@ -3225,21 +3225,21 @@
       <c r="F31" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="89"/>
-      <c r="J31" s="87"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="51"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="27"/>
       <c r="N31" s="31"/>
-      <c r="O31" s="90"/>
+      <c r="O31" s="54"/>
     </row>
     <row r="32" spans="1:15" ht="15.4">
-      <c r="A32" s="77"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="67"/>
+      <c r="A32" s="58"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="66"/>
       <c r="D32" s="24" t="s">
         <v>65</v>
       </c>
@@ -3249,19 +3249,19 @@
       <c r="F32" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G32" s="49"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
+      <c r="G32" s="64"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
       <c r="K32" s="26"/>
       <c r="L32" s="26"/>
       <c r="M32" s="27"/>
       <c r="N32" s="31"/>
-      <c r="O32" s="85"/>
+      <c r="O32" s="49"/>
     </row>
     <row r="33" spans="1:15" ht="15.4">
-      <c r="A33" s="77"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="67"/>
+      <c r="A33" s="58"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="66"/>
       <c r="D33" s="24" t="s">
         <v>66</v>
       </c>
@@ -3271,19 +3271,19 @@
       <c r="F33" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G33" s="49"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
+      <c r="G33" s="64"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="27"/>
       <c r="N33" s="31"/>
-      <c r="O33" s="85"/>
+      <c r="O33" s="49"/>
     </row>
     <row r="34" spans="1:15" ht="15.4">
-      <c r="A34" s="77"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="67"/>
+      <c r="A34" s="58"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="66"/>
       <c r="D34" s="24" t="s">
         <v>67</v>
       </c>
@@ -3293,19 +3293,19 @@
       <c r="F34" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G34" s="49"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
+      <c r="G34" s="64"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
       <c r="M34" s="27"/>
       <c r="N34" s="31"/>
-      <c r="O34" s="85"/>
+      <c r="O34" s="49"/>
     </row>
     <row r="35" spans="1:15" ht="15.4">
-      <c r="A35" s="77"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="67"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="66"/>
       <c r="D35" s="24" t="s">
         <v>68</v>
       </c>
@@ -3315,23 +3315,23 @@
       <c r="F35" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G35" s="49"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
+      <c r="G35" s="64"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
       <c r="K35" s="26"/>
       <c r="L35" s="26"/>
       <c r="M35" s="27"/>
       <c r="N35" s="31"/>
-      <c r="O35" s="85"/>
+      <c r="O35" s="49"/>
     </row>
     <row r="36" spans="1:15" ht="15.4">
-      <c r="A36" s="63" t="s">
+      <c r="A36" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="72" t="s">
+      <c r="B36" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="70" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="33" t="s">
@@ -3343,14 +3343,14 @@
       <c r="F36" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G36" s="68" t="s">
+      <c r="G36" s="67" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15.4">
-      <c r="A37" s="49"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="67"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="66"/>
       <c r="D37" s="33" t="s">
         <v>74</v>
       </c>
@@ -3360,12 +3360,12 @@
       <c r="F37" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G37" s="49"/>
+      <c r="G37" s="64"/>
     </row>
     <row r="38" spans="1:15" ht="15.4">
-      <c r="A38" s="49"/>
-      <c r="B38" s="49"/>
-      <c r="C38" s="67"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="66"/>
       <c r="D38" s="33" t="s">
         <v>76</v>
       </c>
@@ -3375,12 +3375,12 @@
       <c r="F38" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G38" s="49"/>
+      <c r="G38" s="64"/>
     </row>
     <row r="39" spans="1:15" ht="15.4">
-      <c r="A39" s="49"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="67"/>
+      <c r="A39" s="64"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="66"/>
       <c r="D39" s="33" t="s">
         <v>78</v>
       </c>
@@ -3390,12 +3390,12 @@
       <c r="F39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G39" s="49"/>
+      <c r="G39" s="64"/>
     </row>
     <row r="40" spans="1:15" ht="15.4">
-      <c r="A40" s="49"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="67"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="66"/>
       <c r="D40" s="33" t="s">
         <v>79</v>
       </c>
@@ -3405,12 +3405,12 @@
       <c r="F40" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G40" s="49"/>
+      <c r="G40" s="64"/>
     </row>
     <row r="41" spans="1:15" ht="15.4">
-      <c r="A41" s="49"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="67"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="66"/>
       <c r="D41" s="33" t="s">
         <v>81</v>
       </c>
@@ -3420,12 +3420,12 @@
       <c r="F41" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G41" s="49"/>
+      <c r="G41" s="64"/>
     </row>
     <row r="42" spans="1:15" ht="15.4">
-      <c r="A42" s="49"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="67"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="66"/>
       <c r="D42" s="33" t="s">
         <v>82</v>
       </c>
@@ -3435,12 +3435,12 @@
       <c r="F42" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G42" s="49"/>
+      <c r="G42" s="64"/>
     </row>
     <row r="43" spans="1:15" ht="15.4">
-      <c r="A43" s="49"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="67"/>
+      <c r="A43" s="64"/>
+      <c r="B43" s="64"/>
+      <c r="C43" s="66"/>
       <c r="D43" s="33" t="s">
         <v>84</v>
       </c>
@@ -3450,12 +3450,12 @@
       <c r="F43" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G43" s="49"/>
+      <c r="G43" s="64"/>
     </row>
     <row r="44" spans="1:15" ht="15.4">
-      <c r="A44" s="49"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="67"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="66"/>
       <c r="D44" s="33" t="s">
         <v>86</v>
       </c>
@@ -3465,14 +3465,14 @@
       <c r="F44" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G44" s="49"/>
+      <c r="G44" s="64"/>
     </row>
     <row r="45" spans="1:15" ht="15.4">
-      <c r="A45" s="49"/>
-      <c r="B45" s="65" t="s">
+      <c r="A45" s="64"/>
+      <c r="B45" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -3484,14 +3484,14 @@
       <c r="F45" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G45" s="68" t="s">
+      <c r="G45" s="67" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.4">
-      <c r="A46" s="49"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="67"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="66"/>
       <c r="D46" s="33" t="s">
         <v>93</v>
       </c>
@@ -3501,12 +3501,12 @@
       <c r="F46" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G46" s="49"/>
+      <c r="G46" s="64"/>
     </row>
     <row r="47" spans="1:15" ht="15.4">
-      <c r="A47" s="49"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="67"/>
+      <c r="A47" s="64"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="66"/>
       <c r="D47" s="33" t="s">
         <v>95</v>
       </c>
@@ -3516,12 +3516,12 @@
       <c r="F47" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G47" s="49"/>
+      <c r="G47" s="64"/>
     </row>
     <row r="48" spans="1:15" ht="15.4">
-      <c r="A48" s="49"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="67"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="66"/>
       <c r="D48" s="33" t="s">
         <v>97</v>
       </c>
@@ -3531,10 +3531,10 @@
       <c r="F48" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G48" s="49"/>
+      <c r="G48" s="64"/>
     </row>
     <row r="49" spans="1:7" ht="25.5">
-      <c r="A49" s="63" t="s">
+      <c r="A49" s="68" t="s">
         <v>98</v>
       </c>
       <c r="B49" s="33" t="s">
@@ -3557,11 +3557,11 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.4">
-      <c r="A50" s="49"/>
-      <c r="B50" s="65" t="s">
+      <c r="A50" s="64"/>
+      <c r="B50" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="C50" s="66" t="s">
+      <c r="C50" s="70" t="s">
         <v>54</v>
       </c>
       <c r="D50" s="33" t="s">
@@ -3573,14 +3573,14 @@
       <c r="F50" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G50" s="68" t="s">
+      <c r="G50" s="67" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.4">
-      <c r="A51" s="49"/>
-      <c r="B51" s="49"/>
-      <c r="C51" s="67"/>
+      <c r="A51" s="64"/>
+      <c r="B51" s="64"/>
+      <c r="C51" s="66"/>
       <c r="D51" s="33" t="s">
         <v>105</v>
       </c>
@@ -3590,12 +3590,12 @@
       <c r="F51" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G51" s="49"/>
+      <c r="G51" s="64"/>
     </row>
     <row r="52" spans="1:7" ht="15.4">
-      <c r="A52" s="49"/>
-      <c r="B52" s="49"/>
-      <c r="C52" s="67"/>
+      <c r="A52" s="64"/>
+      <c r="B52" s="64"/>
+      <c r="C52" s="66"/>
       <c r="D52" s="33" t="s">
         <v>107</v>
       </c>
@@ -3605,12 +3605,12 @@
       <c r="F52" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G52" s="49"/>
+      <c r="G52" s="64"/>
     </row>
     <row r="53" spans="1:7" ht="15.4">
-      <c r="A53" s="49"/>
-      <c r="B53" s="49"/>
-      <c r="C53" s="67"/>
+      <c r="A53" s="64"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="66"/>
       <c r="D53" s="33" t="s">
         <v>109</v>
       </c>
@@ -3620,12 +3620,12 @@
       <c r="F53" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G53" s="49"/>
+      <c r="G53" s="64"/>
     </row>
     <row r="54" spans="1:7" ht="15.4">
-      <c r="A54" s="49"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="67"/>
+      <c r="A54" s="64"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="66"/>
       <c r="D54" s="33" t="s">
         <v>111</v>
       </c>
@@ -3635,12 +3635,12 @@
       <c r="F54" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G54" s="49"/>
+      <c r="G54" s="64"/>
     </row>
     <row r="55" spans="1:7" ht="15.4">
-      <c r="A55" s="49"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="67"/>
+      <c r="A55" s="64"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="66"/>
       <c r="D55" s="33" t="s">
         <v>113</v>
       </c>
@@ -3650,12 +3650,12 @@
       <c r="F55" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G55" s="49"/>
+      <c r="G55" s="64"/>
     </row>
     <row r="56" spans="1:7" ht="15.4">
-      <c r="A56" s="49"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="67"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="64"/>
+      <c r="C56" s="66"/>
       <c r="D56" s="33" t="s">
         <v>114</v>
       </c>
@@ -3665,12 +3665,12 @@
       <c r="F56" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G56" s="49"/>
+      <c r="G56" s="64"/>
     </row>
     <row r="57" spans="1:7" ht="15.4">
-      <c r="A57" s="49"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="67"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="64"/>
+      <c r="C57" s="66"/>
       <c r="D57" s="33" t="s">
         <v>115</v>
       </c>
@@ -3680,12 +3680,12 @@
       <c r="F57" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G57" s="49"/>
+      <c r="G57" s="64"/>
     </row>
     <row r="58" spans="1:7" ht="15.4">
-      <c r="A58" s="49"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="67"/>
+      <c r="A58" s="64"/>
+      <c r="B58" s="64"/>
+      <c r="C58" s="66"/>
       <c r="D58" s="33" t="s">
         <v>116</v>
       </c>
@@ -3695,12 +3695,12 @@
       <c r="F58" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G58" s="49"/>
+      <c r="G58" s="64"/>
     </row>
     <row r="59" spans="1:7" ht="15.4">
-      <c r="A59" s="49"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="67"/>
+      <c r="A59" s="64"/>
+      <c r="B59" s="64"/>
+      <c r="C59" s="66"/>
       <c r="D59" s="33" t="s">
         <v>117</v>
       </c>
@@ -3710,10 +3710,10 @@
       <c r="F59" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G59" s="49"/>
+      <c r="G59" s="64"/>
     </row>
     <row r="60" spans="1:7" ht="25.5">
-      <c r="A60" s="49"/>
+      <c r="A60" s="64"/>
       <c r="B60" s="33" t="s">
         <v>118</v>
       </c>
@@ -3734,11 +3734,11 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.4">
-      <c r="A61" s="49"/>
-      <c r="B61" s="72" t="s">
+      <c r="A61" s="64"/>
+      <c r="B61" s="69" t="s">
         <v>289</v>
       </c>
-      <c r="C61" s="66" t="s">
+      <c r="C61" s="70" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="33" t="s">
@@ -3750,14 +3750,14 @@
       <c r="F61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G61" s="68" t="s">
+      <c r="G61" s="67" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.4">
-      <c r="A62" s="49"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="67"/>
+      <c r="A62" s="64"/>
+      <c r="B62" s="64"/>
+      <c r="C62" s="66"/>
       <c r="D62" s="33" t="s">
         <v>125</v>
       </c>
@@ -3767,12 +3767,12 @@
       <c r="F62" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G62" s="49"/>
+      <c r="G62" s="64"/>
     </row>
     <row r="63" spans="1:7" ht="25.5">
-      <c r="A63" s="49"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="67"/>
+      <c r="A63" s="64"/>
+      <c r="B63" s="64"/>
+      <c r="C63" s="66"/>
       <c r="D63" s="33" t="s">
         <v>127</v>
       </c>
@@ -3782,12 +3782,12 @@
       <c r="F63" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G63" s="49"/>
+      <c r="G63" s="64"/>
     </row>
     <row r="64" spans="1:7" ht="15.4">
-      <c r="A64" s="49"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="67"/>
+      <c r="A64" s="64"/>
+      <c r="B64" s="64"/>
+      <c r="C64" s="66"/>
       <c r="D64" s="33" t="s">
         <v>128</v>
       </c>
@@ -3797,12 +3797,12 @@
       <c r="F64" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G64" s="49"/>
+      <c r="G64" s="64"/>
     </row>
     <row r="65" spans="1:7" ht="25.5">
-      <c r="A65" s="49"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="67"/>
+      <c r="A65" s="64"/>
+      <c r="B65" s="64"/>
+      <c r="C65" s="66"/>
       <c r="D65" s="33" t="s">
         <v>130</v>
       </c>
@@ -3812,12 +3812,12 @@
       <c r="F65" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G65" s="49"/>
+      <c r="G65" s="64"/>
     </row>
     <row r="66" spans="1:7" ht="25.5">
-      <c r="A66" s="49"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="67"/>
+      <c r="A66" s="64"/>
+      <c r="B66" s="64"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="33" t="s">
         <v>132</v>
       </c>
@@ -3827,14 +3827,14 @@
       <c r="F66" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G66" s="49"/>
+      <c r="G66" s="64"/>
     </row>
     <row r="67" spans="1:7" ht="15.4">
-      <c r="A67" s="49"/>
-      <c r="B67" s="65" t="s">
+      <c r="A67" s="64"/>
+      <c r="B67" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="70" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="33" t="s">
@@ -3846,14 +3846,14 @@
       <c r="F67" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G67" s="68" t="s">
+      <c r="G67" s="67" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.4">
-      <c r="A68" s="49"/>
-      <c r="B68" s="49"/>
-      <c r="C68" s="67"/>
+      <c r="A68" s="64"/>
+      <c r="B68" s="64"/>
+      <c r="C68" s="66"/>
       <c r="D68" s="33" t="s">
         <v>138</v>
       </c>
@@ -3863,12 +3863,12 @@
       <c r="F68" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G68" s="49"/>
+      <c r="G68" s="64"/>
     </row>
     <row r="69" spans="1:7" ht="15.4">
-      <c r="A69" s="49"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="67"/>
+      <c r="A69" s="64"/>
+      <c r="B69" s="64"/>
+      <c r="C69" s="66"/>
       <c r="D69" s="33" t="s">
         <v>140</v>
       </c>
@@ -3878,12 +3878,12 @@
       <c r="F69" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G69" s="49"/>
+      <c r="G69" s="64"/>
     </row>
     <row r="70" spans="1:7" ht="25.5">
-      <c r="A70" s="49"/>
-      <c r="B70" s="49"/>
-      <c r="C70" s="67"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="64"/>
+      <c r="C70" s="66"/>
       <c r="D70" s="33" t="s">
         <v>142</v>
       </c>
@@ -3893,14 +3893,14 @@
       <c r="F70" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G70" s="49"/>
+      <c r="G70" s="64"/>
     </row>
     <row r="71" spans="1:7" ht="15.4">
-      <c r="A71" s="49"/>
-      <c r="B71" s="65" t="s">
+      <c r="A71" s="64"/>
+      <c r="B71" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="C71" s="66" t="s">
+      <c r="C71" s="70" t="s">
         <v>54</v>
       </c>
       <c r="D71" s="33" t="s">
@@ -3912,14 +3912,14 @@
       <c r="F71" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G71" s="68" t="s">
+      <c r="G71" s="67" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.4">
-      <c r="A72" s="49"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="67"/>
+      <c r="A72" s="64"/>
+      <c r="B72" s="64"/>
+      <c r="C72" s="66"/>
       <c r="D72" s="33" t="s">
         <v>148</v>
       </c>
@@ -3929,12 +3929,12 @@
       <c r="F72" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G72" s="49"/>
+      <c r="G72" s="64"/>
     </row>
     <row r="73" spans="1:7" ht="15.4">
-      <c r="A73" s="49"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="67"/>
+      <c r="A73" s="64"/>
+      <c r="B73" s="64"/>
+      <c r="C73" s="66"/>
       <c r="D73" s="33" t="s">
         <v>150</v>
       </c>
@@ -3944,12 +3944,12 @@
       <c r="F73" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G73" s="49"/>
+      <c r="G73" s="64"/>
     </row>
     <row r="74" spans="1:7" ht="25.5">
-      <c r="A74" s="49"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="67"/>
+      <c r="A74" s="64"/>
+      <c r="B74" s="64"/>
+      <c r="C74" s="66"/>
       <c r="D74" s="33" t="s">
         <v>152</v>
       </c>
@@ -3959,12 +3959,12 @@
       <c r="F74" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G74" s="49"/>
+      <c r="G74" s="64"/>
     </row>
     <row r="75" spans="1:7" ht="25.5">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="67"/>
+      <c r="A75" s="64"/>
+      <c r="B75" s="64"/>
+      <c r="C75" s="66"/>
       <c r="D75" s="33" t="s">
         <v>154</v>
       </c>
@@ -3974,14 +3974,14 @@
       <c r="F75" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G75" s="49"/>
+      <c r="G75" s="64"/>
     </row>
     <row r="76" spans="1:7" ht="25.5">
-      <c r="A76" s="49"/>
-      <c r="B76" s="73" t="s">
+      <c r="A76" s="64"/>
+      <c r="B76" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="66" t="s">
+      <c r="C76" s="70" t="s">
         <v>32</v>
       </c>
       <c r="D76" s="33" t="s">
@@ -3991,16 +3991,16 @@
         <v>262</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G76" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="G76" s="67" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.4">
-      <c r="A77" s="49"/>
-      <c r="B77" s="49"/>
-      <c r="C77" s="67"/>
+      <c r="A77" s="64"/>
+      <c r="B77" s="64"/>
+      <c r="C77" s="66"/>
       <c r="D77" s="33" t="s">
         <v>159</v>
       </c>
@@ -4008,14 +4008,14 @@
         <v>160</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G77" s="49"/>
+        <v>284</v>
+      </c>
+      <c r="G77" s="64"/>
     </row>
     <row r="78" spans="1:7" ht="38.25">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="67"/>
+      <c r="A78" s="64"/>
+      <c r="B78" s="64"/>
+      <c r="C78" s="66"/>
       <c r="D78" s="33" t="s">
         <v>161</v>
       </c>
@@ -4023,14 +4023,14 @@
         <v>162</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G78" s="49"/>
+        <v>284</v>
+      </c>
+      <c r="G78" s="64"/>
     </row>
     <row r="79" spans="1:7" ht="38.25">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="67"/>
+      <c r="A79" s="64"/>
+      <c r="B79" s="64"/>
+      <c r="C79" s="66"/>
       <c r="D79" s="33" t="s">
         <v>163</v>
       </c>
@@ -4038,14 +4038,14 @@
         <v>263</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G79" s="49"/>
+        <v>284</v>
+      </c>
+      <c r="G79" s="64"/>
     </row>
     <row r="80" spans="1:7" ht="15.4">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="67"/>
+      <c r="A80" s="64"/>
+      <c r="B80" s="64"/>
+      <c r="C80" s="66"/>
       <c r="D80" s="33" t="s">
         <v>164</v>
       </c>
@@ -4053,12 +4053,12 @@
         <v>165</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G80" s="49"/>
+        <v>284</v>
+      </c>
+      <c r="G80" s="64"/>
     </row>
     <row r="81" spans="1:7" ht="25.5">
-      <c r="A81" s="63" t="s">
+      <c r="A81" s="68" t="s">
         <v>280</v>
       </c>
       <c r="B81" s="33" t="s">
@@ -4081,11 +4081,11 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.4">
-      <c r="A82" s="49"/>
-      <c r="B82" s="65" t="s">
+      <c r="A82" s="64"/>
+      <c r="B82" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="66" t="s">
+      <c r="C82" s="70" t="s">
         <v>54</v>
       </c>
       <c r="D82" s="33" t="s">
@@ -4097,14 +4097,14 @@
       <c r="F82" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G82" s="68" t="s">
+      <c r="G82" s="67" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.4">
-      <c r="A83" s="49"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="67"/>
+      <c r="A83" s="64"/>
+      <c r="B83" s="64"/>
+      <c r="C83" s="66"/>
       <c r="D83" s="33" t="s">
         <v>174</v>
       </c>
@@ -4114,12 +4114,12 @@
       <c r="F83" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G83" s="49"/>
+      <c r="G83" s="64"/>
     </row>
     <row r="84" spans="1:7" ht="15.4">
-      <c r="A84" s="49"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="67"/>
+      <c r="A84" s="64"/>
+      <c r="B84" s="64"/>
+      <c r="C84" s="66"/>
       <c r="D84" s="33" t="s">
         <v>176</v>
       </c>
@@ -4129,12 +4129,12 @@
       <c r="F84" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G84" s="49"/>
+      <c r="G84" s="64"/>
     </row>
     <row r="85" spans="1:7" ht="15.4">
-      <c r="A85" s="49"/>
-      <c r="B85" s="49"/>
-      <c r="C85" s="67"/>
+      <c r="A85" s="64"/>
+      <c r="B85" s="64"/>
+      <c r="C85" s="66"/>
       <c r="D85" s="33" t="s">
         <v>177</v>
       </c>
@@ -4144,14 +4144,14 @@
       <c r="F85" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G85" s="49"/>
+      <c r="G85" s="64"/>
     </row>
     <row r="86" spans="1:7" ht="15.4">
-      <c r="A86" s="49"/>
-      <c r="B86" s="65" t="s">
+      <c r="A86" s="64"/>
+      <c r="B86" s="71" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="66" t="s">
+      <c r="C86" s="70" t="s">
         <v>62</v>
       </c>
       <c r="D86" s="33" t="s">
@@ -4163,14 +4163,14 @@
       <c r="F86" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G86" s="68" t="s">
+      <c r="G86" s="67" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="25.5">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="67"/>
+      <c r="A87" s="64"/>
+      <c r="B87" s="64"/>
+      <c r="C87" s="66"/>
       <c r="D87" s="33" t="s">
         <v>181</v>
       </c>
@@ -4180,12 +4180,12 @@
       <c r="F87" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G87" s="49"/>
+      <c r="G87" s="64"/>
     </row>
     <row r="88" spans="1:7" ht="25.5">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="67"/>
+      <c r="A88" s="64"/>
+      <c r="B88" s="64"/>
+      <c r="C88" s="66"/>
       <c r="D88" s="33" t="s">
         <v>183</v>
       </c>
@@ -4195,14 +4195,14 @@
       <c r="F88" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G88" s="49"/>
+      <c r="G88" s="64"/>
     </row>
     <row r="89" spans="1:7" ht="25.5">
-      <c r="A89" s="49"/>
-      <c r="B89" s="65" t="s">
+      <c r="A89" s="64"/>
+      <c r="B89" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="C89" s="66" t="s">
+      <c r="C89" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D89" s="33" t="s">
@@ -4214,14 +4214,14 @@
       <c r="F89" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G89" s="70" t="s">
+      <c r="G89" s="73" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.4">
-      <c r="A90" s="49"/>
-      <c r="B90" s="49"/>
-      <c r="C90" s="67"/>
+      <c r="A90" s="64"/>
+      <c r="B90" s="64"/>
+      <c r="C90" s="66"/>
       <c r="D90" s="33" t="s">
         <v>188</v>
       </c>
@@ -4231,14 +4231,14 @@
       <c r="F90" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G90" s="64"/>
+      <c r="G90" s="74"/>
     </row>
     <row r="91" spans="1:7" ht="15.4">
-      <c r="A91" s="49"/>
-      <c r="B91" s="71" t="s">
+      <c r="A91" s="64"/>
+      <c r="B91" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="66" t="s">
+      <c r="C91" s="70" t="s">
         <v>32</v>
       </c>
       <c r="D91" s="33" t="s">
@@ -4250,14 +4250,14 @@
       <c r="F91" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G91" s="68" t="s">
+      <c r="G91" s="67" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.4">
-      <c r="A92" s="49"/>
-      <c r="B92" s="49"/>
-      <c r="C92" s="67"/>
+      <c r="A92" s="64"/>
+      <c r="B92" s="64"/>
+      <c r="C92" s="66"/>
       <c r="D92" s="33" t="s">
         <v>193</v>
       </c>
@@ -4267,12 +4267,12 @@
       <c r="F92" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G92" s="49"/>
+      <c r="G92" s="64"/>
     </row>
     <row r="93" spans="1:7" ht="15.4">
-      <c r="A93" s="49"/>
-      <c r="B93" s="49"/>
-      <c r="C93" s="67"/>
+      <c r="A93" s="64"/>
+      <c r="B93" s="64"/>
+      <c r="C93" s="66"/>
       <c r="D93" s="33" t="s">
         <v>195</v>
       </c>
@@ -4282,12 +4282,12 @@
       <c r="F93" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G93" s="49"/>
+      <c r="G93" s="64"/>
     </row>
     <row r="94" spans="1:7" ht="15.4">
-      <c r="A94" s="49"/>
-      <c r="B94" s="49"/>
-      <c r="C94" s="67"/>
+      <c r="A94" s="64"/>
+      <c r="B94" s="64"/>
+      <c r="C94" s="66"/>
       <c r="D94" s="33" t="s">
         <v>197</v>
       </c>
@@ -4297,12 +4297,12 @@
       <c r="F94" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G94" s="49"/>
+      <c r="G94" s="64"/>
     </row>
     <row r="95" spans="1:7" ht="15.4">
-      <c r="A95" s="49"/>
-      <c r="B95" s="49"/>
-      <c r="C95" s="67"/>
+      <c r="A95" s="64"/>
+      <c r="B95" s="64"/>
+      <c r="C95" s="66"/>
       <c r="D95" s="33" t="s">
         <v>198</v>
       </c>
@@ -4312,14 +4312,14 @@
       <c r="F95" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G95" s="49"/>
+      <c r="G95" s="64"/>
     </row>
     <row r="96" spans="1:7" ht="15.4">
-      <c r="A96" s="49"/>
-      <c r="B96" s="65" t="s">
+      <c r="A96" s="64"/>
+      <c r="B96" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="C96" s="66" t="s">
+      <c r="C96" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D96" s="33" t="s">
@@ -4331,14 +4331,14 @@
       <c r="F96" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G96" s="68" t="s">
+      <c r="G96" s="67" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15.4">
-      <c r="A97" s="49"/>
-      <c r="B97" s="49"/>
-      <c r="C97" s="67"/>
+      <c r="A97" s="64"/>
+      <c r="B97" s="64"/>
+      <c r="C97" s="66"/>
       <c r="D97" s="33" t="s">
         <v>203</v>
       </c>
@@ -4348,16 +4348,16 @@
       <c r="F97" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G97" s="49"/>
+      <c r="G97" s="64"/>
     </row>
     <row r="98" spans="1:7" ht="15.4">
-      <c r="A98" s="63" t="s">
+      <c r="A98" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="B98" s="65" t="s">
+      <c r="B98" s="71" t="s">
         <v>206</v>
       </c>
-      <c r="C98" s="66" t="s">
+      <c r="C98" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D98" s="33" t="s">
@@ -4369,14 +4369,14 @@
       <c r="F98" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G98" s="68" t="s">
+      <c r="G98" s="67" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15.4">
-      <c r="A99" s="49"/>
-      <c r="B99" s="49"/>
-      <c r="C99" s="67"/>
+      <c r="A99" s="64"/>
+      <c r="B99" s="64"/>
+      <c r="C99" s="66"/>
       <c r="D99" s="33" t="s">
         <v>209</v>
       </c>
@@ -4386,14 +4386,14 @@
       <c r="F99" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G99" s="49"/>
+      <c r="G99" s="64"/>
     </row>
     <row r="100" spans="1:7" ht="15.4">
-      <c r="A100" s="49"/>
-      <c r="B100" s="65" t="s">
+      <c r="A100" s="64"/>
+      <c r="B100" s="71" t="s">
         <v>211</v>
       </c>
-      <c r="C100" s="66" t="s">
+      <c r="C100" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="33" t="s">
@@ -4405,12 +4405,12 @@
       <c r="F100" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G100" s="49"/>
+      <c r="G100" s="64"/>
     </row>
     <row r="101" spans="1:7" ht="15.4">
-      <c r="A101" s="49"/>
-      <c r="B101" s="49"/>
-      <c r="C101" s="67"/>
+      <c r="A101" s="64"/>
+      <c r="B101" s="64"/>
+      <c r="C101" s="66"/>
       <c r="D101" s="33" t="s">
         <v>213</v>
       </c>
@@ -4420,14 +4420,14 @@
       <c r="F101" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G101" s="49"/>
+      <c r="G101" s="64"/>
     </row>
     <row r="102" spans="1:7" ht="25.5">
-      <c r="A102" s="49"/>
-      <c r="B102" s="65" t="s">
+      <c r="A102" s="64"/>
+      <c r="B102" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="C102" s="66" t="s">
+      <c r="C102" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D102" s="33" t="s">
@@ -4439,12 +4439,12 @@
       <c r="F102" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G102" s="49"/>
+      <c r="G102" s="64"/>
     </row>
     <row r="103" spans="1:7" ht="25.5">
-      <c r="A103" s="49"/>
-      <c r="B103" s="49"/>
-      <c r="C103" s="67"/>
+      <c r="A103" s="64"/>
+      <c r="B103" s="64"/>
+      <c r="C103" s="66"/>
       <c r="D103" s="33" t="s">
         <v>216</v>
       </c>
@@ -4454,12 +4454,12 @@
       <c r="F103" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G103" s="49"/>
+      <c r="G103" s="64"/>
     </row>
     <row r="104" spans="1:7" ht="15.4">
-      <c r="A104" s="49"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="67"/>
+      <c r="A104" s="64"/>
+      <c r="B104" s="64"/>
+      <c r="C104" s="66"/>
       <c r="D104" s="33" t="s">
         <v>218</v>
       </c>
@@ -4469,12 +4469,12 @@
       <c r="F104" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G104" s="49"/>
+      <c r="G104" s="64"/>
     </row>
     <row r="105" spans="1:7" ht="25.5">
-      <c r="A105" s="49"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="67"/>
+      <c r="A105" s="64"/>
+      <c r="B105" s="64"/>
+      <c r="C105" s="66"/>
       <c r="D105" s="33" t="s">
         <v>219</v>
       </c>
@@ -4484,12 +4484,12 @@
       <c r="F105" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G105" s="49"/>
+      <c r="G105" s="64"/>
     </row>
     <row r="106" spans="1:7" ht="25.5">
-      <c r="A106" s="49"/>
-      <c r="B106" s="49"/>
-      <c r="C106" s="67"/>
+      <c r="A106" s="64"/>
+      <c r="B106" s="64"/>
+      <c r="C106" s="66"/>
       <c r="D106" s="33" t="s">
         <v>220</v>
       </c>
@@ -4499,12 +4499,12 @@
       <c r="F106" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G106" s="49"/>
+      <c r="G106" s="64"/>
     </row>
     <row r="107" spans="1:7" ht="15.4">
-      <c r="A107" s="49"/>
-      <c r="B107" s="49"/>
-      <c r="C107" s="67"/>
+      <c r="A107" s="64"/>
+      <c r="B107" s="64"/>
+      <c r="C107" s="66"/>
       <c r="D107" s="33" t="s">
         <v>221</v>
       </c>
@@ -4514,16 +4514,16 @@
       <c r="F107" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G107" s="49"/>
+      <c r="G107" s="64"/>
     </row>
     <row r="108" spans="1:7" ht="15.4">
-      <c r="A108" s="63" t="s">
+      <c r="A108" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="B108" s="65" t="s">
+      <c r="B108" s="71" t="s">
         <v>223</v>
       </c>
-      <c r="C108" s="66" t="s">
+      <c r="C108" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D108" s="33" t="s">
@@ -4535,14 +4535,14 @@
       <c r="F108" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G108" s="68" t="s">
+      <c r="G108" s="67" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15.4">
-      <c r="A109" s="49"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="67"/>
+      <c r="A109" s="64"/>
+      <c r="B109" s="64"/>
+      <c r="C109" s="66"/>
       <c r="D109" s="33" t="s">
         <v>226</v>
       </c>
@@ -4552,14 +4552,14 @@
       <c r="F109" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G109" s="49"/>
+      <c r="G109" s="64"/>
     </row>
     <row r="110" spans="1:7" ht="25.5">
-      <c r="A110" s="49"/>
-      <c r="B110" s="65" t="s">
+      <c r="A110" s="64"/>
+      <c r="B110" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="C110" s="66" t="s">
+      <c r="C110" s="70" t="s">
         <v>54</v>
       </c>
       <c r="D110" s="33" t="s">
@@ -4571,12 +4571,12 @@
       <c r="F110" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G110" s="49"/>
+      <c r="G110" s="64"/>
     </row>
     <row r="111" spans="1:7" ht="15.4">
-      <c r="A111" s="49"/>
-      <c r="B111" s="49"/>
-      <c r="C111" s="67"/>
+      <c r="A111" s="64"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="66"/>
       <c r="D111" s="33" t="s">
         <v>230</v>
       </c>
@@ -4586,14 +4586,14 @@
       <c r="F111" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G111" s="49"/>
+      <c r="G111" s="64"/>
     </row>
     <row r="112" spans="1:7" ht="15.4">
-      <c r="A112" s="49"/>
-      <c r="B112" s="65" t="s">
+      <c r="A112" s="64"/>
+      <c r="B112" s="71" t="s">
         <v>232</v>
       </c>
-      <c r="C112" s="66" t="s">
+      <c r="C112" s="70" t="s">
         <v>89</v>
       </c>
       <c r="D112" s="33" t="s">
@@ -4605,12 +4605,12 @@
       <c r="F112" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G112" s="49"/>
+      <c r="G112" s="64"/>
     </row>
     <row r="113" spans="1:7" ht="15.4">
-      <c r="A113" s="49"/>
-      <c r="B113" s="49"/>
-      <c r="C113" s="67"/>
+      <c r="A113" s="64"/>
+      <c r="B113" s="64"/>
+      <c r="C113" s="66"/>
       <c r="D113" s="33" t="s">
         <v>234</v>
       </c>
@@ -4620,14 +4620,14 @@
       <c r="F113" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G113" s="49"/>
+      <c r="G113" s="64"/>
     </row>
     <row r="114" spans="1:7" ht="25.5">
-      <c r="A114" s="49"/>
-      <c r="B114" s="65" t="s">
+      <c r="A114" s="64"/>
+      <c r="B114" s="71" t="s">
         <v>235</v>
       </c>
-      <c r="C114" s="66" t="s">
+      <c r="C114" s="70" t="s">
         <v>54</v>
       </c>
       <c r="D114" s="33" t="s">
@@ -4639,12 +4639,12 @@
       <c r="F114" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G114" s="49"/>
+      <c r="G114" s="64"/>
     </row>
     <row r="115" spans="1:7" ht="15.4">
-      <c r="A115" s="64"/>
-      <c r="B115" s="64"/>
-      <c r="C115" s="69"/>
+      <c r="A115" s="74"/>
+      <c r="B115" s="74"/>
+      <c r="C115" s="76"/>
       <c r="D115" s="38" t="s">
         <v>237</v>
       </c>
@@ -4654,10 +4654,10 @@
       <c r="F115" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G115" s="64"/>
+      <c r="G115" s="74"/>
     </row>
     <row r="116" spans="1:7" ht="15.4">
-      <c r="A116" s="53" t="s">
+      <c r="A116" s="81" t="s">
         <v>239</v>
       </c>
       <c r="B116" s="39" t="s">
@@ -4675,12 +4675,12 @@
       <c r="F116" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G116" s="52" t="s">
+      <c r="G116" s="80" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.4">
-      <c r="A117" s="54"/>
+      <c r="A117" s="82"/>
       <c r="B117" s="41" t="s">
         <v>244</v>
       </c>
@@ -4696,10 +4696,10 @@
       <c r="F117" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G117" s="54"/>
+      <c r="G117" s="82"/>
     </row>
     <row r="118" spans="1:7" ht="15.4">
-      <c r="A118" s="54"/>
+      <c r="A118" s="82"/>
       <c r="B118" s="41" t="s">
         <v>247</v>
       </c>
@@ -4715,7 +4715,7 @@
       <c r="F118" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G118" s="54"/>
+      <c r="G118" s="82"/>
     </row>
     <row r="119" spans="1:7" ht="15.4">
       <c r="A119" s="42"/>
@@ -5025,33 +5025,47 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="O19:O24"/>
-    <mergeCell ref="I25:I30"/>
-    <mergeCell ref="J25:J30"/>
-    <mergeCell ref="O25:O30"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="J31:J35"/>
-    <mergeCell ref="O31:O35"/>
-    <mergeCell ref="I19:I24"/>
-    <mergeCell ref="J19:J24"/>
-    <mergeCell ref="H19:H24"/>
-    <mergeCell ref="A19:A35"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="G19:G24"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="G25:G30"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="A36:A48"/>
-    <mergeCell ref="B36:B44"/>
-    <mergeCell ref="C36:C44"/>
-    <mergeCell ref="G36:G44"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="G14:G18"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="G116:G118"/>
+    <mergeCell ref="C3:C13"/>
+    <mergeCell ref="B3:B18"/>
+    <mergeCell ref="A3:A18"/>
+    <mergeCell ref="A108:A115"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="G108:G115"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="A98:A107"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="G98:G107"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B102:B107"/>
+    <mergeCell ref="C102:C107"/>
+    <mergeCell ref="A81:A97"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="G86:G88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="C91:C95"/>
+    <mergeCell ref="G91:G95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="G96:G97"/>
     <mergeCell ref="A49:A80"/>
     <mergeCell ref="B50:B59"/>
     <mergeCell ref="C50:C59"/>
@@ -5068,47 +5082,33 @@
     <mergeCell ref="B76:B80"/>
     <mergeCell ref="C76:C80"/>
     <mergeCell ref="G76:G80"/>
-    <mergeCell ref="A81:A97"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="G82:G85"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="G86:G88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="C91:C95"/>
-    <mergeCell ref="G91:G95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="A98:A107"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="G98:G107"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B102:B107"/>
-    <mergeCell ref="C102:C107"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="G14:G18"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="G116:G118"/>
-    <mergeCell ref="C3:C13"/>
-    <mergeCell ref="B3:B18"/>
-    <mergeCell ref="A3:A18"/>
-    <mergeCell ref="A108:A115"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="G108:G115"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="B36:B44"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="H19:H24"/>
+    <mergeCell ref="A19:A35"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="G19:G24"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="O19:O24"/>
+    <mergeCell ref="I25:I30"/>
+    <mergeCell ref="J25:J30"/>
+    <mergeCell ref="O25:O30"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="J31:J35"/>
+    <mergeCell ref="O31:O35"/>
+    <mergeCell ref="I19:I24"/>
+    <mergeCell ref="J19:J24"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <dataValidations count="2">

--- a/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
+++ b/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Develop\others\MyPGEE\main\408\ds\【数据结构应用题】打卡表及参考文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFBB20B-E30E-474E-B3BA-585ACE3844BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0EEBC2-4D4E-4614-95F4-79DD7990F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4074,7 +4074,7 @@
         <v>168</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G81" s="30" t="s">
         <v>169</v>
@@ -4095,7 +4095,7 @@
         <v>172</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G82" s="67" t="s">
         <v>173</v>
@@ -4112,7 +4112,7 @@
         <v>175</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G83" s="64"/>
     </row>
@@ -4127,7 +4127,7 @@
         <v>264</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G84" s="64"/>
     </row>
@@ -4142,7 +4142,7 @@
         <v>265</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G85" s="64"/>
     </row>
@@ -4161,7 +4161,7 @@
         <v>266</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G86" s="67" t="s">
         <v>180</v>
@@ -4178,7 +4178,7 @@
         <v>182</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G87" s="64"/>
     </row>
@@ -4193,7 +4193,7 @@
         <v>184</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G88" s="64"/>
     </row>

--- a/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
+++ b/main/408/ds/【数据结构应用题】打卡表及参考文档/数据结构强化打卡表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Develop\others\MyPGEE\main\408\ds\【数据结构应用题】打卡表及参考文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0EEBC2-4D4E-4614-95F4-79DD7990F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EF813C-836A-400A-A8A2-7456D23BC362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2182,95 +2182,11 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2307,6 +2223,90 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2673,13 +2673,13 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="55" t="s">
         <v>251</v>
       </c>
       <c r="D3" s="14" t="s">
@@ -2696,9 +2696,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.4">
-      <c r="A4" s="89"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="64"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="14" t="s">
         <v>12</v>
       </c>
@@ -2711,9 +2711,9 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
-      <c r="A5" s="89"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="64"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="14" t="s">
         <v>14</v>
       </c>
@@ -2726,9 +2726,9 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" ht="15.4">
-      <c r="A6" s="89"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="64"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
@@ -2741,9 +2741,9 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" ht="15.4">
-      <c r="A7" s="89"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="64"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="14" t="s">
         <v>18</v>
       </c>
@@ -2756,9 +2756,9 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" ht="15.4">
-      <c r="A8" s="90"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="84"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="14" t="s">
         <v>20</v>
       </c>
@@ -2771,9 +2771,9 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
-      <c r="A9" s="89"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="64"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="14" t="s">
         <v>22</v>
       </c>
@@ -2786,9 +2786,9 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" ht="15.4">
-      <c r="A10" s="89"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="64"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="14" t="s">
         <v>24</v>
       </c>
@@ -2801,9 +2801,9 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" ht="15.4">
-      <c r="A11" s="89"/>
-      <c r="B11" s="86"/>
-      <c r="C11" s="64"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="14" t="s">
         <v>26</v>
       </c>
@@ -2816,9 +2816,9 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" ht="15.4">
-      <c r="A12" s="89"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="64"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="14" t="s">
         <v>28</v>
       </c>
@@ -2831,9 +2831,9 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" ht="15.4">
-      <c r="A13" s="89"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="64"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="14" t="s">
         <v>30</v>
       </c>
@@ -2846,9 +2846,9 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7" ht="15.4">
-      <c r="A14" s="89"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="77" t="s">
+      <c r="A14" s="61"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="48" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -2860,14 +2860,14 @@
       <c r="F14" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G14" s="79" t="s">
+      <c r="G14" s="51" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.4">
-      <c r="A15" s="89"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="64"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13" t="s">
         <v>36</v>
       </c>
@@ -2877,12 +2877,12 @@
       <c r="F15" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G15" s="64"/>
+      <c r="G15" s="49"/>
     </row>
     <row r="16" spans="1:7" ht="15.4">
-      <c r="A16" s="90"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="78"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="13" t="s">
         <v>38</v>
       </c>
@@ -2892,12 +2892,12 @@
       <c r="F16" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G16" s="80"/>
+      <c r="G16" s="52"/>
     </row>
     <row r="17" spans="1:15" ht="15.4">
-      <c r="A17" s="90"/>
-      <c r="B17" s="87"/>
-      <c r="C17" s="78"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
@@ -2907,12 +2907,12 @@
       <c r="F17" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G17" s="80"/>
+      <c r="G17" s="52"/>
     </row>
     <row r="18" spans="1:15" ht="15.4">
-      <c r="A18" s="89"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="64"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="49"/>
       <c r="D18" s="13" t="s">
         <v>42</v>
       </c>
@@ -2922,16 +2922,16 @@
       <c r="F18" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G18" s="64"/>
+      <c r="G18" s="49"/>
     </row>
     <row r="19" spans="1:15" ht="16.149999999999999">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="76" t="s">
         <v>282</v>
       </c>
-      <c r="B19" s="59" t="s">
+      <c r="B19" s="78" t="s">
         <v>281</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C19" s="79" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="20" t="s">
@@ -2943,22 +2943,22 @@
       <c r="F19" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="55"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="51"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="87"/>
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
       <c r="M19" s="22"/>
       <c r="N19" s="23"/>
-      <c r="O19" s="48"/>
+      <c r="O19" s="84"/>
     </row>
     <row r="20" spans="1:15" ht="15.4">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="61"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="24" t="s">
         <v>46</v>
       </c>
@@ -2968,20 +2968,20 @@
       <c r="F20" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G20" s="58"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="22"/>
       <c r="N20" s="23"/>
-      <c r="O20" s="49"/>
+      <c r="O20" s="85"/>
     </row>
     <row r="21" spans="1:15" ht="15.4">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="61"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="24" t="s">
         <v>48</v>
       </c>
@@ -2991,20 +2991,20 @@
       <c r="F21" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G21" s="58"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
       <c r="M21" s="22"/>
       <c r="N21" s="23"/>
-      <c r="O21" s="49"/>
+      <c r="O21" s="85"/>
     </row>
     <row r="22" spans="1:15" ht="15.4">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="61"/>
+      <c r="A22" s="77"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="24" t="s">
         <v>50</v>
       </c>
@@ -3014,20 +3014,20 @@
       <c r="F22" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G22" s="58"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="22"/>
       <c r="N22" s="23"/>
-      <c r="O22" s="49"/>
+      <c r="O22" s="85"/>
     </row>
     <row r="23" spans="1:15" ht="15.4">
-      <c r="A23" s="58"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="61"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="24" t="s">
         <v>52</v>
       </c>
@@ -3037,20 +3037,20 @@
       <c r="F23" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G23" s="58"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="M23" s="27"/>
       <c r="N23" s="23"/>
-      <c r="O23" s="49"/>
+      <c r="O23" s="85"/>
     </row>
     <row r="24" spans="1:15" ht="15.4">
-      <c r="A24" s="58"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="61"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="24" t="s">
         <v>53</v>
       </c>
@@ -3060,22 +3060,22 @@
       <c r="F24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G24" s="58"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
       <c r="M24" s="22"/>
       <c r="N24" s="23"/>
-      <c r="O24" s="49"/>
+      <c r="O24" s="85"/>
     </row>
     <row r="25" spans="1:15" ht="15.4">
-      <c r="A25" s="58"/>
-      <c r="B25" s="63" t="s">
+      <c r="A25" s="77"/>
+      <c r="B25" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="C25" s="65" t="s">
+      <c r="C25" s="83" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="29" t="s">
@@ -3087,21 +3087,21 @@
       <c r="F25" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="50"/>
-      <c r="J25" s="51"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="87"/>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="22"/>
       <c r="N25" s="23"/>
-      <c r="O25" s="48"/>
+      <c r="O25" s="84"/>
     </row>
     <row r="26" spans="1:15" ht="15.4">
-      <c r="A26" s="58"/>
-      <c r="B26" s="64"/>
-      <c r="C26" s="66"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="67"/>
       <c r="D26" s="24" t="s">
         <v>57</v>
       </c>
@@ -3111,19 +3111,19 @@
       <c r="F26" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="52"/>
+      <c r="G26" s="49"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="88"/>
       <c r="K26" s="26"/>
       <c r="L26" s="26"/>
       <c r="M26" s="22"/>
       <c r="N26" s="23"/>
-      <c r="O26" s="49"/>
+      <c r="O26" s="85"/>
     </row>
     <row r="27" spans="1:15" ht="15.4">
-      <c r="A27" s="58"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="66"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="67"/>
       <c r="D27" s="24" t="s">
         <v>58</v>
       </c>
@@ -3133,19 +3133,19 @@
       <c r="F27" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="52"/>
+      <c r="G27" s="49"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="88"/>
       <c r="K27" s="26"/>
       <c r="L27" s="26"/>
       <c r="M27" s="22"/>
       <c r="N27" s="23"/>
-      <c r="O27" s="49"/>
+      <c r="O27" s="85"/>
     </row>
     <row r="28" spans="1:15" ht="15.4">
-      <c r="A28" s="58"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="66"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="67"/>
       <c r="D28" s="24" t="s">
         <v>59</v>
       </c>
@@ -3155,19 +3155,19 @@
       <c r="F28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="52"/>
+      <c r="G28" s="49"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="88"/>
       <c r="K28" s="26"/>
       <c r="L28" s="26"/>
       <c r="M28" s="22"/>
       <c r="N28" s="23"/>
-      <c r="O28" s="49"/>
+      <c r="O28" s="85"/>
     </row>
     <row r="29" spans="1:15" ht="15.4">
-      <c r="A29" s="58"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="66"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="67"/>
       <c r="D29" s="24" t="s">
         <v>60</v>
       </c>
@@ -3177,19 +3177,19 @@
       <c r="F29" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G29" s="64"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="52"/>
+      <c r="G29" s="49"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="88"/>
       <c r="K29" s="26"/>
       <c r="L29" s="26"/>
       <c r="M29" s="27"/>
       <c r="N29" s="23"/>
-      <c r="O29" s="49"/>
+      <c r="O29" s="85"/>
     </row>
     <row r="30" spans="1:15" ht="15.4">
-      <c r="A30" s="58"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="66"/>
+      <c r="A30" s="77"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="67"/>
       <c r="D30" s="24" t="s">
         <v>61</v>
       </c>
@@ -3199,21 +3199,21 @@
       <c r="F30" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="52"/>
+      <c r="G30" s="49"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="88"/>
       <c r="K30" s="26"/>
       <c r="L30" s="26"/>
       <c r="M30" s="27"/>
       <c r="N30" s="23"/>
-      <c r="O30" s="49"/>
+      <c r="O30" s="85"/>
     </row>
     <row r="31" spans="1:15" ht="15.4">
-      <c r="A31" s="58"/>
-      <c r="B31" s="64" t="s">
+      <c r="A31" s="77"/>
+      <c r="B31" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="65" t="s">
+      <c r="C31" s="83" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="29" t="s">
@@ -3225,21 +3225,21 @@
       <c r="F31" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G31" s="67" t="s">
+      <c r="G31" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="53"/>
-      <c r="J31" s="51"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="87"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="27"/>
       <c r="N31" s="31"/>
-      <c r="O31" s="54"/>
+      <c r="O31" s="90"/>
     </row>
     <row r="32" spans="1:15" ht="15.4">
-      <c r="A32" s="58"/>
-      <c r="B32" s="64"/>
-      <c r="C32" s="66"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="67"/>
       <c r="D32" s="24" t="s">
         <v>65</v>
       </c>
@@ -3249,19 +3249,19 @@
       <c r="F32" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
       <c r="K32" s="26"/>
       <c r="L32" s="26"/>
       <c r="M32" s="27"/>
       <c r="N32" s="31"/>
-      <c r="O32" s="49"/>
+      <c r="O32" s="85"/>
     </row>
     <row r="33" spans="1:15" ht="15.4">
-      <c r="A33" s="58"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="66"/>
+      <c r="A33" s="77"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="67"/>
       <c r="D33" s="24" t="s">
         <v>66</v>
       </c>
@@ -3271,19 +3271,19 @@
       <c r="F33" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G33" s="64"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="27"/>
       <c r="N33" s="31"/>
-      <c r="O33" s="49"/>
+      <c r="O33" s="85"/>
     </row>
     <row r="34" spans="1:15" ht="15.4">
-      <c r="A34" s="58"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="66"/>
+      <c r="A34" s="77"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="67"/>
       <c r="D34" s="24" t="s">
         <v>67</v>
       </c>
@@ -3293,19 +3293,19 @@
       <c r="F34" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G34" s="64"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
       <c r="M34" s="27"/>
       <c r="N34" s="31"/>
-      <c r="O34" s="49"/>
+      <c r="O34" s="85"/>
     </row>
     <row r="35" spans="1:15" ht="15.4">
-      <c r="A35" s="58"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="66"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="67"/>
       <c r="D35" s="24" t="s">
         <v>68</v>
       </c>
@@ -3315,23 +3315,23 @@
       <c r="F35" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G35" s="64"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
       <c r="K35" s="26"/>
       <c r="L35" s="26"/>
       <c r="M35" s="27"/>
       <c r="N35" s="31"/>
-      <c r="O35" s="49"/>
+      <c r="O35" s="85"/>
     </row>
     <row r="36" spans="1:15" ht="15.4">
-      <c r="A36" s="68" t="s">
+      <c r="A36" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="66" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="33" t="s">
@@ -3343,14 +3343,14 @@
       <c r="F36" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G36" s="67" t="s">
+      <c r="G36" s="68" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15.4">
-      <c r="A37" s="64"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="66"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="67"/>
       <c r="D37" s="33" t="s">
         <v>74</v>
       </c>
@@ -3360,12 +3360,12 @@
       <c r="F37" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G37" s="64"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" spans="1:15" ht="15.4">
-      <c r="A38" s="64"/>
-      <c r="B38" s="64"/>
-      <c r="C38" s="66"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="67"/>
       <c r="D38" s="33" t="s">
         <v>76</v>
       </c>
@@ -3375,12 +3375,12 @@
       <c r="F38" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G38" s="64"/>
+      <c r="G38" s="49"/>
     </row>
     <row r="39" spans="1:15" ht="15.4">
-      <c r="A39" s="64"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="66"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="67"/>
       <c r="D39" s="33" t="s">
         <v>78</v>
       </c>
@@ -3390,12 +3390,12 @@
       <c r="F39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G39" s="64"/>
+      <c r="G39" s="49"/>
     </row>
     <row r="40" spans="1:15" ht="15.4">
-      <c r="A40" s="64"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="66"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="67"/>
       <c r="D40" s="33" t="s">
         <v>79</v>
       </c>
@@ -3405,12 +3405,12 @@
       <c r="F40" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G40" s="64"/>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="1:15" ht="15.4">
-      <c r="A41" s="64"/>
-      <c r="B41" s="64"/>
-      <c r="C41" s="66"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="67"/>
       <c r="D41" s="33" t="s">
         <v>81</v>
       </c>
@@ -3420,12 +3420,12 @@
       <c r="F41" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G41" s="64"/>
+      <c r="G41" s="49"/>
     </row>
     <row r="42" spans="1:15" ht="15.4">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="66"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="67"/>
       <c r="D42" s="33" t="s">
         <v>82</v>
       </c>
@@ -3435,12 +3435,12 @@
       <c r="F42" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G42" s="64"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="1:15" ht="15.4">
-      <c r="A43" s="64"/>
-      <c r="B43" s="64"/>
-      <c r="C43" s="66"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="67"/>
       <c r="D43" s="33" t="s">
         <v>84</v>
       </c>
@@ -3450,12 +3450,12 @@
       <c r="F43" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G43" s="64"/>
+      <c r="G43" s="49"/>
     </row>
     <row r="44" spans="1:15" ht="15.4">
-      <c r="A44" s="64"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="66"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="67"/>
       <c r="D44" s="33" t="s">
         <v>86</v>
       </c>
@@ -3465,14 +3465,14 @@
       <c r="F44" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G44" s="64"/>
+      <c r="G44" s="49"/>
     </row>
     <row r="45" spans="1:15" ht="15.4">
-      <c r="A45" s="64"/>
-      <c r="B45" s="71" t="s">
+      <c r="A45" s="49"/>
+      <c r="B45" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="70" t="s">
+      <c r="C45" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -3484,14 +3484,14 @@
       <c r="F45" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G45" s="67" t="s">
+      <c r="G45" s="68" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.4">
-      <c r="A46" s="64"/>
-      <c r="B46" s="64"/>
-      <c r="C46" s="66"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="67"/>
       <c r="D46" s="33" t="s">
         <v>93</v>
       </c>
@@ -3501,12 +3501,12 @@
       <c r="F46" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G46" s="64"/>
+      <c r="G46" s="49"/>
     </row>
     <row r="47" spans="1:15" ht="15.4">
-      <c r="A47" s="64"/>
-      <c r="B47" s="64"/>
-      <c r="C47" s="66"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="67"/>
       <c r="D47" s="33" t="s">
         <v>95</v>
       </c>
@@ -3516,12 +3516,12 @@
       <c r="F47" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G47" s="64"/>
+      <c r="G47" s="49"/>
     </row>
     <row r="48" spans="1:15" ht="15.4">
-      <c r="A48" s="64"/>
-      <c r="B48" s="64"/>
-      <c r="C48" s="66"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="67"/>
       <c r="D48" s="33" t="s">
         <v>97</v>
       </c>
@@ -3531,10 +3531,10 @@
       <c r="F48" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G48" s="64"/>
+      <c r="G48" s="49"/>
     </row>
     <row r="49" spans="1:7" ht="25.5">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="63" t="s">
         <v>98</v>
       </c>
       <c r="B49" s="33" t="s">
@@ -3557,11 +3557,11 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.4">
-      <c r="A50" s="64"/>
-      <c r="B50" s="71" t="s">
+      <c r="A50" s="49"/>
+      <c r="B50" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="C50" s="70" t="s">
+      <c r="C50" s="66" t="s">
         <v>54</v>
       </c>
       <c r="D50" s="33" t="s">
@@ -3573,14 +3573,14 @@
       <c r="F50" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G50" s="67" t="s">
+      <c r="G50" s="68" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.4">
-      <c r="A51" s="64"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="66"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="67"/>
       <c r="D51" s="33" t="s">
         <v>105</v>
       </c>
@@ -3590,12 +3590,12 @@
       <c r="F51" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G51" s="64"/>
+      <c r="G51" s="49"/>
     </row>
     <row r="52" spans="1:7" ht="15.4">
-      <c r="A52" s="64"/>
-      <c r="B52" s="64"/>
-      <c r="C52" s="66"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="67"/>
       <c r="D52" s="33" t="s">
         <v>107</v>
       </c>
@@ -3605,12 +3605,12 @@
       <c r="F52" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G52" s="64"/>
+      <c r="G52" s="49"/>
     </row>
     <row r="53" spans="1:7" ht="15.4">
-      <c r="A53" s="64"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="66"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="67"/>
       <c r="D53" s="33" t="s">
         <v>109</v>
       </c>
@@ -3620,12 +3620,12 @@
       <c r="F53" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G53" s="64"/>
+      <c r="G53" s="49"/>
     </row>
     <row r="54" spans="1:7" ht="15.4">
-      <c r="A54" s="64"/>
-      <c r="B54" s="64"/>
-      <c r="C54" s="66"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="67"/>
       <c r="D54" s="33" t="s">
         <v>111</v>
       </c>
@@ -3635,12 +3635,12 @@
       <c r="F54" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G54" s="64"/>
+      <c r="G54" s="49"/>
     </row>
     <row r="55" spans="1:7" ht="15.4">
-      <c r="A55" s="64"/>
-      <c r="B55" s="64"/>
-      <c r="C55" s="66"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="67"/>
       <c r="D55" s="33" t="s">
         <v>113</v>
       </c>
@@ -3650,12 +3650,12 @@
       <c r="F55" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G55" s="64"/>
+      <c r="G55" s="49"/>
     </row>
     <row r="56" spans="1:7" ht="15.4">
-      <c r="A56" s="64"/>
-      <c r="B56" s="64"/>
-      <c r="C56" s="66"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="67"/>
       <c r="D56" s="33" t="s">
         <v>114</v>
       </c>
@@ -3665,12 +3665,12 @@
       <c r="F56" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G56" s="64"/>
+      <c r="G56" s="49"/>
     </row>
     <row r="57" spans="1:7" ht="15.4">
-      <c r="A57" s="64"/>
-      <c r="B57" s="64"/>
-      <c r="C57" s="66"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="67"/>
       <c r="D57" s="33" t="s">
         <v>115</v>
       </c>
@@ -3680,12 +3680,12 @@
       <c r="F57" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G57" s="64"/>
+      <c r="G57" s="49"/>
     </row>
     <row r="58" spans="1:7" ht="15.4">
-      <c r="A58" s="64"/>
-      <c r="B58" s="64"/>
-      <c r="C58" s="66"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="67"/>
       <c r="D58" s="33" t="s">
         <v>116</v>
       </c>
@@ -3695,12 +3695,12 @@
       <c r="F58" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G58" s="64"/>
+      <c r="G58" s="49"/>
     </row>
     <row r="59" spans="1:7" ht="15.4">
-      <c r="A59" s="64"/>
-      <c r="B59" s="64"/>
-      <c r="C59" s="66"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="67"/>
       <c r="D59" s="33" t="s">
         <v>117</v>
       </c>
@@ -3710,10 +3710,10 @@
       <c r="F59" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G59" s="64"/>
+      <c r="G59" s="49"/>
     </row>
     <row r="60" spans="1:7" ht="25.5">
-      <c r="A60" s="64"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="33" t="s">
         <v>118</v>
       </c>
@@ -3734,11 +3734,11 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.4">
-      <c r="A61" s="64"/>
-      <c r="B61" s="69" t="s">
+      <c r="A61" s="49"/>
+      <c r="B61" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="C61" s="70" t="s">
+      <c r="C61" s="66" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="33" t="s">
@@ -3750,14 +3750,14 @@
       <c r="F61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G61" s="67" t="s">
+      <c r="G61" s="68" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.4">
-      <c r="A62" s="64"/>
-      <c r="B62" s="64"/>
-      <c r="C62" s="66"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="67"/>
       <c r="D62" s="33" t="s">
         <v>125</v>
       </c>
@@ -3767,12 +3767,12 @@
       <c r="F62" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G62" s="64"/>
+      <c r="G62" s="49"/>
     </row>
     <row r="63" spans="1:7" ht="25.5">
-      <c r="A63" s="64"/>
-      <c r="B63" s="64"/>
-      <c r="C63" s="66"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="67"/>
       <c r="D63" s="33" t="s">
         <v>127</v>
       </c>
@@ -3782,12 +3782,12 @@
       <c r="F63" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G63" s="64"/>
+      <c r="G63" s="49"/>
     </row>
     <row r="64" spans="1:7" ht="15.4">
-      <c r="A64" s="64"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="66"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="67"/>
       <c r="D64" s="33" t="s">
         <v>128</v>
       </c>
@@ -3797,12 +3797,12 @@
       <c r="F64" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G64" s="64"/>
+      <c r="G64" s="49"/>
     </row>
     <row r="65" spans="1:7" ht="25.5">
-      <c r="A65" s="64"/>
-      <c r="B65" s="64"/>
-      <c r="C65" s="66"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="67"/>
       <c r="D65" s="33" t="s">
         <v>130</v>
       </c>
@@ -3812,12 +3812,12 @@
       <c r="F65" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G65" s="64"/>
+      <c r="G65" s="49"/>
     </row>
     <row r="66" spans="1:7" ht="25.5">
-      <c r="A66" s="64"/>
-      <c r="B66" s="64"/>
-      <c r="C66" s="66"/>
+      <c r="A66" s="49"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="67"/>
       <c r="D66" s="33" t="s">
         <v>132</v>
       </c>
@@ -3827,14 +3827,14 @@
       <c r="F66" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G66" s="64"/>
+      <c r="G66" s="49"/>
     </row>
     <row r="67" spans="1:7" ht="15.4">
-      <c r="A67" s="64"/>
-      <c r="B67" s="71" t="s">
+      <c r="A67" s="49"/>
+      <c r="B67" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="70" t="s">
+      <c r="C67" s="66" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="33" t="s">
@@ -3846,14 +3846,14 @@
       <c r="F67" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G67" s="67" t="s">
+      <c r="G67" s="68" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.4">
-      <c r="A68" s="64"/>
-      <c r="B68" s="64"/>
-      <c r="C68" s="66"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="67"/>
       <c r="D68" s="33" t="s">
         <v>138</v>
       </c>
@@ -3863,12 +3863,12 @@
       <c r="F68" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G68" s="64"/>
+      <c r="G68" s="49"/>
     </row>
     <row r="69" spans="1:7" ht="15.4">
-      <c r="A69" s="64"/>
-      <c r="B69" s="64"/>
-      <c r="C69" s="66"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="67"/>
       <c r="D69" s="33" t="s">
         <v>140</v>
       </c>
@@ -3878,12 +3878,12 @@
       <c r="F69" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G69" s="64"/>
+      <c r="G69" s="49"/>
     </row>
     <row r="70" spans="1:7" ht="25.5">
-      <c r="A70" s="64"/>
-      <c r="B70" s="64"/>
-      <c r="C70" s="66"/>
+      <c r="A70" s="49"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="67"/>
       <c r="D70" s="33" t="s">
         <v>142</v>
       </c>
@@ -3893,14 +3893,14 @@
       <c r="F70" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G70" s="64"/>
+      <c r="G70" s="49"/>
     </row>
     <row r="71" spans="1:7" ht="15.4">
-      <c r="A71" s="64"/>
-      <c r="B71" s="71" t="s">
+      <c r="A71" s="49"/>
+      <c r="B71" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="C71" s="70" t="s">
+      <c r="C71" s="66" t="s">
         <v>54</v>
       </c>
       <c r="D71" s="33" t="s">
@@ -3912,14 +3912,14 @@
       <c r="F71" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G71" s="67" t="s">
+      <c r="G71" s="68" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.4">
-      <c r="A72" s="64"/>
-      <c r="B72" s="64"/>
-      <c r="C72" s="66"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="67"/>
       <c r="D72" s="33" t="s">
         <v>148</v>
       </c>
@@ -3929,12 +3929,12 @@
       <c r="F72" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G72" s="64"/>
+      <c r="G72" s="49"/>
     </row>
     <row r="73" spans="1:7" ht="15.4">
-      <c r="A73" s="64"/>
-      <c r="B73" s="64"/>
-      <c r="C73" s="66"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="67"/>
       <c r="D73" s="33" t="s">
         <v>150</v>
       </c>
@@ -3944,12 +3944,12 @@
       <c r="F73" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G73" s="64"/>
+      <c r="G73" s="49"/>
     </row>
     <row r="74" spans="1:7" ht="25.5">
-      <c r="A74" s="64"/>
-      <c r="B74" s="64"/>
-      <c r="C74" s="66"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="67"/>
       <c r="D74" s="33" t="s">
         <v>152</v>
       </c>
@@ -3959,12 +3959,12 @@
       <c r="F74" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G74" s="64"/>
+      <c r="G74" s="49"/>
     </row>
     <row r="75" spans="1:7" ht="25.5">
-      <c r="A75" s="64"/>
-      <c r="B75" s="64"/>
-      <c r="C75" s="66"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="67"/>
       <c r="D75" s="33" t="s">
         <v>154</v>
       </c>
@@ -3974,14 +3974,14 @@
       <c r="F75" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G75" s="64"/>
+      <c r="G75" s="49"/>
     </row>
     <row r="76" spans="1:7" ht="25.5">
-      <c r="A76" s="64"/>
-      <c r="B76" s="72" t="s">
+      <c r="A76" s="49"/>
+      <c r="B76" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="70" t="s">
+      <c r="C76" s="66" t="s">
         <v>32</v>
       </c>
       <c r="D76" s="33" t="s">
@@ -3993,14 +3993,14 @@
       <c r="F76" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G76" s="67" t="s">
+      <c r="G76" s="68" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.4">
-      <c r="A77" s="64"/>
-      <c r="B77" s="64"/>
-      <c r="C77" s="66"/>
+      <c r="A77" s="49"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="67"/>
       <c r="D77" s="33" t="s">
         <v>159</v>
       </c>
@@ -4010,12 +4010,12 @@
       <c r="F77" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G77" s="64"/>
+      <c r="G77" s="49"/>
     </row>
     <row r="78" spans="1:7" ht="38.25">
-      <c r="A78" s="64"/>
-      <c r="B78" s="64"/>
-      <c r="C78" s="66"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="67"/>
       <c r="D78" s="33" t="s">
         <v>161</v>
       </c>
@@ -4025,12 +4025,12 @@
       <c r="F78" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G78" s="64"/>
+      <c r="G78" s="49"/>
     </row>
     <row r="79" spans="1:7" ht="38.25">
-      <c r="A79" s="64"/>
-      <c r="B79" s="64"/>
-      <c r="C79" s="66"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="67"/>
       <c r="D79" s="33" t="s">
         <v>163</v>
       </c>
@@ -4040,12 +4040,12 @@
       <c r="F79" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G79" s="64"/>
+      <c r="G79" s="49"/>
     </row>
     <row r="80" spans="1:7" ht="15.4">
-      <c r="A80" s="64"/>
-      <c r="B80" s="64"/>
-      <c r="C80" s="66"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="67"/>
       <c r="D80" s="33" t="s">
         <v>164</v>
       </c>
@@ -4055,10 +4055,10 @@
       <c r="F80" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G80" s="64"/>
+      <c r="G80" s="49"/>
     </row>
     <row r="81" spans="1:7" ht="25.5">
-      <c r="A81" s="68" t="s">
+      <c r="A81" s="63" t="s">
         <v>280</v>
       </c>
       <c r="B81" s="33" t="s">
@@ -4081,11 +4081,11 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.4">
-      <c r="A82" s="64"/>
-      <c r="B82" s="71" t="s">
+      <c r="A82" s="49"/>
+      <c r="B82" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="70" t="s">
+      <c r="C82" s="66" t="s">
         <v>54</v>
       </c>
       <c r="D82" s="33" t="s">
@@ -4097,14 +4097,14 @@
       <c r="F82" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G82" s="67" t="s">
+      <c r="G82" s="68" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.4">
-      <c r="A83" s="64"/>
-      <c r="B83" s="64"/>
-      <c r="C83" s="66"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="67"/>
       <c r="D83" s="33" t="s">
         <v>174</v>
       </c>
@@ -4114,12 +4114,12 @@
       <c r="F83" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G83" s="64"/>
+      <c r="G83" s="49"/>
     </row>
     <row r="84" spans="1:7" ht="15.4">
-      <c r="A84" s="64"/>
-      <c r="B84" s="64"/>
-      <c r="C84" s="66"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="67"/>
       <c r="D84" s="33" t="s">
         <v>176</v>
       </c>
@@ -4129,12 +4129,12 @@
       <c r="F84" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G84" s="64"/>
+      <c r="G84" s="49"/>
     </row>
     <row r="85" spans="1:7" ht="15.4">
-      <c r="A85" s="64"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="66"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="67"/>
       <c r="D85" s="33" t="s">
         <v>177</v>
       </c>
@@ -4144,14 +4144,14 @@
       <c r="F85" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G85" s="64"/>
+      <c r="G85" s="49"/>
     </row>
     <row r="86" spans="1:7" ht="15.4">
-      <c r="A86" s="64"/>
-      <c r="B86" s="71" t="s">
+      <c r="A86" s="49"/>
+      <c r="B86" s="65" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="70" t="s">
+      <c r="C86" s="66" t="s">
         <v>62</v>
       </c>
       <c r="D86" s="33" t="s">
@@ -4163,14 +4163,14 @@
       <c r="F86" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G86" s="67" t="s">
+      <c r="G86" s="68" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="25.5">
-      <c r="A87" s="64"/>
-      <c r="B87" s="64"/>
-      <c r="C87" s="66"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="67"/>
       <c r="D87" s="33" t="s">
         <v>181</v>
       </c>
@@ -4180,12 +4180,12 @@
       <c r="F87" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G87" s="64"/>
+      <c r="G87" s="49"/>
     </row>
     <row r="88" spans="1:7" ht="25.5">
-      <c r="A88" s="64"/>
-      <c r="B88" s="64"/>
-      <c r="C88" s="66"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="67"/>
       <c r="D88" s="33" t="s">
         <v>183</v>
       </c>
@@ -4195,14 +4195,14 @@
       <c r="F88" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G88" s="64"/>
+      <c r="G88" s="49"/>
     </row>
     <row r="89" spans="1:7" ht="25.5">
-      <c r="A89" s="64"/>
-      <c r="B89" s="71" t="s">
+      <c r="A89" s="49"/>
+      <c r="B89" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="C89" s="70" t="s">
+      <c r="C89" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D89" s="33" t="s">
@@ -4212,16 +4212,16 @@
         <v>267</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G89" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="G89" s="70" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.4">
-      <c r="A90" s="64"/>
-      <c r="B90" s="64"/>
-      <c r="C90" s="66"/>
+      <c r="A90" s="49"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="67"/>
       <c r="D90" s="33" t="s">
         <v>188</v>
       </c>
@@ -4229,16 +4229,16 @@
         <v>189</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G90" s="74"/>
+        <v>284</v>
+      </c>
+      <c r="G90" s="64"/>
     </row>
     <row r="91" spans="1:7" ht="15.4">
-      <c r="A91" s="64"/>
-      <c r="B91" s="75" t="s">
+      <c r="A91" s="49"/>
+      <c r="B91" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="70" t="s">
+      <c r="C91" s="66" t="s">
         <v>32</v>
       </c>
       <c r="D91" s="33" t="s">
@@ -4248,16 +4248,16 @@
         <v>268</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G91" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="G91" s="68" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.4">
-      <c r="A92" s="64"/>
-      <c r="B92" s="64"/>
-      <c r="C92" s="66"/>
+      <c r="A92" s="49"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="67"/>
       <c r="D92" s="33" t="s">
         <v>193</v>
       </c>
@@ -4265,14 +4265,14 @@
         <v>194</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G92" s="64"/>
+        <v>284</v>
+      </c>
+      <c r="G92" s="49"/>
     </row>
     <row r="93" spans="1:7" ht="15.4">
-      <c r="A93" s="64"/>
-      <c r="B93" s="64"/>
-      <c r="C93" s="66"/>
+      <c r="A93" s="49"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="67"/>
       <c r="D93" s="33" t="s">
         <v>195</v>
       </c>
@@ -4280,14 +4280,14 @@
         <v>196</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G93" s="64"/>
+        <v>284</v>
+      </c>
+      <c r="G93" s="49"/>
     </row>
     <row r="94" spans="1:7" ht="15.4">
-      <c r="A94" s="64"/>
-      <c r="B94" s="64"/>
-      <c r="C94" s="66"/>
+      <c r="A94" s="49"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="67"/>
       <c r="D94" s="33" t="s">
         <v>197</v>
       </c>
@@ -4295,14 +4295,14 @@
         <v>269</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G94" s="64"/>
+        <v>284</v>
+      </c>
+      <c r="G94" s="49"/>
     </row>
     <row r="95" spans="1:7" ht="15.4">
-      <c r="A95" s="64"/>
-      <c r="B95" s="64"/>
-      <c r="C95" s="66"/>
+      <c r="A95" s="49"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="67"/>
       <c r="D95" s="33" t="s">
         <v>198</v>
       </c>
@@ -4310,16 +4310,16 @@
         <v>199</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G95" s="64"/>
+        <v>284</v>
+      </c>
+      <c r="G95" s="49"/>
     </row>
     <row r="96" spans="1:7" ht="15.4">
-      <c r="A96" s="64"/>
-      <c r="B96" s="71" t="s">
+      <c r="A96" s="49"/>
+      <c r="B96" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="C96" s="70" t="s">
+      <c r="C96" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D96" s="33" t="s">
@@ -4329,16 +4329,16 @@
         <v>270</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G96" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="G96" s="68" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15.4">
-      <c r="A97" s="64"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="66"/>
+      <c r="A97" s="49"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="67"/>
       <c r="D97" s="33" t="s">
         <v>203</v>
       </c>
@@ -4346,18 +4346,18 @@
         <v>204</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G97" s="64"/>
+        <v>284</v>
+      </c>
+      <c r="G97" s="49"/>
     </row>
     <row r="98" spans="1:7" ht="15.4">
-      <c r="A98" s="68" t="s">
+      <c r="A98" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="B98" s="71" t="s">
+      <c r="B98" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="C98" s="70" t="s">
+      <c r="C98" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D98" s="33" t="s">
@@ -4369,14 +4369,14 @@
       <c r="F98" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G98" s="67" t="s">
+      <c r="G98" s="68" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15.4">
-      <c r="A99" s="64"/>
-      <c r="B99" s="64"/>
-      <c r="C99" s="66"/>
+      <c r="A99" s="49"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="67"/>
       <c r="D99" s="33" t="s">
         <v>209</v>
       </c>
@@ -4386,14 +4386,14 @@
       <c r="F99" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G99" s="64"/>
+      <c r="G99" s="49"/>
     </row>
     <row r="100" spans="1:7" ht="15.4">
-      <c r="A100" s="64"/>
-      <c r="B100" s="71" t="s">
+      <c r="A100" s="49"/>
+      <c r="B100" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="C100" s="70" t="s">
+      <c r="C100" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="33" t="s">
@@ -4405,12 +4405,12 @@
       <c r="F100" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G100" s="64"/>
+      <c r="G100" s="49"/>
     </row>
     <row r="101" spans="1:7" ht="15.4">
-      <c r="A101" s="64"/>
-      <c r="B101" s="64"/>
-      <c r="C101" s="66"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="67"/>
       <c r="D101" s="33" t="s">
         <v>213</v>
       </c>
@@ -4420,14 +4420,14 @@
       <c r="F101" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G101" s="64"/>
+      <c r="G101" s="49"/>
     </row>
     <row r="102" spans="1:7" ht="25.5">
-      <c r="A102" s="64"/>
-      <c r="B102" s="71" t="s">
+      <c r="A102" s="49"/>
+      <c r="B102" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="C102" s="70" t="s">
+      <c r="C102" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D102" s="33" t="s">
@@ -4439,12 +4439,12 @@
       <c r="F102" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G102" s="64"/>
+      <c r="G102" s="49"/>
     </row>
     <row r="103" spans="1:7" ht="25.5">
-      <c r="A103" s="64"/>
-      <c r="B103" s="64"/>
-      <c r="C103" s="66"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="67"/>
       <c r="D103" s="33" t="s">
         <v>216</v>
       </c>
@@ -4454,12 +4454,12 @@
       <c r="F103" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G103" s="64"/>
+      <c r="G103" s="49"/>
     </row>
     <row r="104" spans="1:7" ht="15.4">
-      <c r="A104" s="64"/>
-      <c r="B104" s="64"/>
-      <c r="C104" s="66"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="67"/>
       <c r="D104" s="33" t="s">
         <v>218</v>
       </c>
@@ -4469,12 +4469,12 @@
       <c r="F104" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G104" s="64"/>
+      <c r="G104" s="49"/>
     </row>
     <row r="105" spans="1:7" ht="25.5">
-      <c r="A105" s="64"/>
-      <c r="B105" s="64"/>
-      <c r="C105" s="66"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="67"/>
       <c r="D105" s="33" t="s">
         <v>219</v>
       </c>
@@ -4484,12 +4484,12 @@
       <c r="F105" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G105" s="64"/>
+      <c r="G105" s="49"/>
     </row>
     <row r="106" spans="1:7" ht="25.5">
-      <c r="A106" s="64"/>
-      <c r="B106" s="64"/>
-      <c r="C106" s="66"/>
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="67"/>
       <c r="D106" s="33" t="s">
         <v>220</v>
       </c>
@@ -4499,12 +4499,12 @@
       <c r="F106" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G106" s="64"/>
+      <c r="G106" s="49"/>
     </row>
     <row r="107" spans="1:7" ht="15.4">
-      <c r="A107" s="64"/>
-      <c r="B107" s="64"/>
-      <c r="C107" s="66"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="67"/>
       <c r="D107" s="33" t="s">
         <v>221</v>
       </c>
@@ -4514,16 +4514,16 @@
       <c r="F107" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G107" s="64"/>
+      <c r="G107" s="49"/>
     </row>
     <row r="108" spans="1:7" ht="15.4">
-      <c r="A108" s="68" t="s">
+      <c r="A108" s="63" t="s">
         <v>222</v>
       </c>
-      <c r="B108" s="71" t="s">
+      <c r="B108" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="C108" s="70" t="s">
+      <c r="C108" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D108" s="33" t="s">
@@ -4535,14 +4535,14 @@
       <c r="F108" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G108" s="67" t="s">
+      <c r="G108" s="68" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15.4">
-      <c r="A109" s="64"/>
-      <c r="B109" s="64"/>
-      <c r="C109" s="66"/>
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="67"/>
       <c r="D109" s="33" t="s">
         <v>226</v>
       </c>
@@ -4552,14 +4552,14 @@
       <c r="F109" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G109" s="64"/>
+      <c r="G109" s="49"/>
     </row>
     <row r="110" spans="1:7" ht="25.5">
-      <c r="A110" s="64"/>
-      <c r="B110" s="71" t="s">
+      <c r="A110" s="49"/>
+      <c r="B110" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="C110" s="70" t="s">
+      <c r="C110" s="66" t="s">
         <v>54</v>
       </c>
       <c r="D110" s="33" t="s">
@@ -4571,12 +4571,12 @@
       <c r="F110" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G110" s="64"/>
+      <c r="G110" s="49"/>
     </row>
     <row r="111" spans="1:7" ht="15.4">
-      <c r="A111" s="64"/>
-      <c r="B111" s="64"/>
-      <c r="C111" s="66"/>
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="67"/>
       <c r="D111" s="33" t="s">
         <v>230</v>
       </c>
@@ -4586,14 +4586,14 @@
       <c r="F111" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G111" s="64"/>
+      <c r="G111" s="49"/>
     </row>
     <row r="112" spans="1:7" ht="15.4">
-      <c r="A112" s="64"/>
-      <c r="B112" s="71" t="s">
+      <c r="A112" s="49"/>
+      <c r="B112" s="65" t="s">
         <v>232</v>
       </c>
-      <c r="C112" s="70" t="s">
+      <c r="C112" s="66" t="s">
         <v>89</v>
       </c>
       <c r="D112" s="33" t="s">
@@ -4605,12 +4605,12 @@
       <c r="F112" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G112" s="64"/>
+      <c r="G112" s="49"/>
     </row>
     <row r="113" spans="1:7" ht="15.4">
-      <c r="A113" s="64"/>
-      <c r="B113" s="64"/>
-      <c r="C113" s="66"/>
+      <c r="A113" s="49"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="67"/>
       <c r="D113" s="33" t="s">
         <v>234</v>
       </c>
@@ -4620,14 +4620,14 @@
       <c r="F113" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G113" s="64"/>
+      <c r="G113" s="49"/>
     </row>
     <row r="114" spans="1:7" ht="25.5">
-      <c r="A114" s="64"/>
-      <c r="B114" s="71" t="s">
+      <c r="A114" s="49"/>
+      <c r="B114" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="C114" s="70" t="s">
+      <c r="C114" s="66" t="s">
         <v>54</v>
       </c>
       <c r="D114" s="33" t="s">
@@ -4639,12 +4639,12 @@
       <c r="F114" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G114" s="64"/>
+      <c r="G114" s="49"/>
     </row>
     <row r="115" spans="1:7" ht="15.4">
-      <c r="A115" s="74"/>
-      <c r="B115" s="74"/>
-      <c r="C115" s="76"/>
+      <c r="A115" s="64"/>
+      <c r="B115" s="64"/>
+      <c r="C115" s="69"/>
       <c r="D115" s="38" t="s">
         <v>237</v>
       </c>
@@ -4654,10 +4654,10 @@
       <c r="F115" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G115" s="74"/>
+      <c r="G115" s="64"/>
     </row>
     <row r="116" spans="1:7" ht="15.4">
-      <c r="A116" s="81" t="s">
+      <c r="A116" s="53" t="s">
         <v>239</v>
       </c>
       <c r="B116" s="39" t="s">
@@ -4675,12 +4675,12 @@
       <c r="F116" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G116" s="80" t="s">
+      <c r="G116" s="52" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.4">
-      <c r="A117" s="82"/>
+      <c r="A117" s="54"/>
       <c r="B117" s="41" t="s">
         <v>244</v>
       </c>
@@ -4696,10 +4696,10 @@
       <c r="F117" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G117" s="82"/>
+      <c r="G117" s="54"/>
     </row>
     <row r="118" spans="1:7" ht="15.4">
-      <c r="A118" s="82"/>
+      <c r="A118" s="54"/>
       <c r="B118" s="41" t="s">
         <v>247</v>
       </c>
@@ -4715,7 +4715,7 @@
       <c r="F118" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G118" s="82"/>
+      <c r="G118" s="54"/>
     </row>
     <row r="119" spans="1:7" ht="15.4">
       <c r="A119" s="42"/>
@@ -5025,6 +5025,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="O19:O24"/>
+    <mergeCell ref="I25:I30"/>
+    <mergeCell ref="J25:J30"/>
+    <mergeCell ref="O25:O30"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="J31:J35"/>
+    <mergeCell ref="O31:O35"/>
+    <mergeCell ref="I19:I24"/>
+    <mergeCell ref="J19:J24"/>
+    <mergeCell ref="H19:H24"/>
+    <mergeCell ref="A19:A35"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="G19:G24"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="B36:B44"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="A49:A80"/>
+    <mergeCell ref="B50:B59"/>
+    <mergeCell ref="C50:C59"/>
+    <mergeCell ref="G50:G59"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="G61:G66"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="B71:B75"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="G76:G80"/>
+    <mergeCell ref="A81:A97"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="G86:G88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="C91:C95"/>
+    <mergeCell ref="G91:G95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="A98:A107"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="G98:G107"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B102:B107"/>
+    <mergeCell ref="C102:C107"/>
     <mergeCell ref="C14:C18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="A116:A118"/>
@@ -5041,74 +5109,6 @@
     <mergeCell ref="B112:B113"/>
     <mergeCell ref="C112:C113"/>
     <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="A98:A107"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="G98:G107"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B102:B107"/>
-    <mergeCell ref="C102:C107"/>
-    <mergeCell ref="A81:A97"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="G82:G85"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="G86:G88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="C91:C95"/>
-    <mergeCell ref="G91:G95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="A49:A80"/>
-    <mergeCell ref="B50:B59"/>
-    <mergeCell ref="C50:C59"/>
-    <mergeCell ref="G50:G59"/>
-    <mergeCell ref="B61:B66"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="G61:G66"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="G76:G80"/>
-    <mergeCell ref="A36:A48"/>
-    <mergeCell ref="B36:B44"/>
-    <mergeCell ref="C36:C44"/>
-    <mergeCell ref="G36:G44"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="G45:G48"/>
-    <mergeCell ref="H19:H24"/>
-    <mergeCell ref="A19:A35"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="G19:G24"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="G25:G30"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="O19:O24"/>
-    <mergeCell ref="I25:I30"/>
-    <mergeCell ref="J25:J30"/>
-    <mergeCell ref="O25:O30"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="J31:J35"/>
-    <mergeCell ref="O31:O35"/>
-    <mergeCell ref="I19:I24"/>
-    <mergeCell ref="J19:J24"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <dataValidations count="2">
